--- a/research/traditional_assets/database/data/peru/peru_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_beverage_alcoholic.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09047399430661504</v>
+        <v>0.09023882102341052</v>
       </c>
       <c r="C2">
-        <v>7582.134795835911</v>
+        <v>7531.128426871166</v>
       </c>
       <c r="D2">
-        <v>7347.434795835911</v>
+        <v>7372.342426871166</v>
       </c>
       <c r="E2">
-        <v>-58.9</v>
+        <v>17.014</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>75.914</v>
       </c>
       <c r="G2">
         <v>234.7</v>
@@ -1582,28 +1582,28 @@
         <v>785.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.8184742</v>
       </c>
       <c r="N2">
-        <v>785.8</v>
+        <v>781.9815258</v>
       </c>
       <c r="O2">
-        <v>231.811</v>
+        <v>230.684550111</v>
       </c>
       <c r="P2">
-        <v>553.989</v>
+        <v>551.296975689</v>
       </c>
       <c r="Q2">
-        <v>656.489</v>
+        <v>653.796975689</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09047399430661504</v>
+        <v>0.09079212729637426</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6960139000637589</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>205.7890033668422</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09023882102341052</v>
+        <v>0.09000364774020601</v>
       </c>
       <c r="C3">
-        <v>7531.128426871166</v>
+        <v>7480.291504893729</v>
       </c>
       <c r="D3">
-        <v>7372.342426871166</v>
+        <v>7397.41950489373</v>
       </c>
       <c r="E3">
-        <v>17.014</v>
+        <v>92.928</v>
       </c>
       <c r="F3">
-        <v>75.914</v>
+        <v>151.828</v>
       </c>
       <c r="G3">
         <v>234.7</v>
@@ -1664,28 +1664,28 @@
         <v>785.8</v>
       </c>
       <c r="M3">
-        <v>3.8184742</v>
+        <v>7.6369484</v>
       </c>
       <c r="N3">
-        <v>781.9815258</v>
+        <v>778.1630515999999</v>
       </c>
       <c r="O3">
-        <v>230.684550111</v>
+        <v>229.558100222</v>
       </c>
       <c r="P3">
-        <v>551.296975689</v>
+        <v>548.6049513779999</v>
       </c>
       <c r="Q3">
-        <v>653.796975689</v>
+        <v>651.1049513779999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09079212729637426</v>
+        <v>0.09111675279612858</v>
       </c>
       <c r="T3">
-        <v>0.6960139000637589</v>
+        <v>0.7010357533016776</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>205.7890033668422</v>
+        <v>102.8945016834211</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09000364774020601</v>
+        <v>0.08976847445700149</v>
       </c>
       <c r="C4">
-        <v>7480.291504893729</v>
+        <v>7429.625764930905</v>
       </c>
       <c r="D4">
-        <v>7397.41950489373</v>
+        <v>7422.667764930906</v>
       </c>
       <c r="E4">
-        <v>92.928</v>
+        <v>168.842</v>
       </c>
       <c r="F4">
-        <v>151.828</v>
+        <v>227.742</v>
       </c>
       <c r="G4">
         <v>234.7</v>
@@ -1746,28 +1746,28 @@
         <v>785.8</v>
       </c>
       <c r="M4">
-        <v>7.6369484</v>
+        <v>11.4554226</v>
       </c>
       <c r="N4">
-        <v>778.1630515999999</v>
+        <v>774.3445773999999</v>
       </c>
       <c r="O4">
-        <v>229.558100222</v>
+        <v>228.431650333</v>
       </c>
       <c r="P4">
-        <v>548.6049513779999</v>
+        <v>545.9129270669999</v>
       </c>
       <c r="Q4">
-        <v>651.1049513779999</v>
+        <v>648.4129270669999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09111675279612858</v>
+        <v>0.09144807160515618</v>
       </c>
       <c r="T4">
-        <v>0.7010357533016776</v>
+        <v>0.7061611499053265</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.8945016834211</v>
+        <v>68.59633445561407</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08976847445700149</v>
+        <v>0.08953330117379696</v>
       </c>
       <c r="C5">
-        <v>7429.625764930905</v>
+        <v>7379.132965778528</v>
       </c>
       <c r="D5">
-        <v>7422.667764930906</v>
+        <v>7448.088965778528</v>
       </c>
       <c r="E5">
-        <v>168.842</v>
+        <v>244.756</v>
       </c>
       <c r="F5">
-        <v>227.742</v>
+        <v>303.656</v>
       </c>
       <c r="G5">
         <v>234.7</v>
@@ -1828,28 +1828,28 @@
         <v>785.8</v>
       </c>
       <c r="M5">
-        <v>11.4554226</v>
+        <v>15.2738968</v>
       </c>
       <c r="N5">
-        <v>774.3445773999999</v>
+        <v>770.5261032</v>
       </c>
       <c r="O5">
-        <v>228.431650333</v>
+        <v>227.305200444</v>
       </c>
       <c r="P5">
-        <v>545.9129270669999</v>
+        <v>543.220902756</v>
       </c>
       <c r="Q5">
-        <v>648.4129270669999</v>
+        <v>645.720902756</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09144807160515618</v>
+        <v>0.09178629288937185</v>
       </c>
       <c r="T5">
-        <v>0.7061611499053265</v>
+        <v>0.7113933256048848</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.59633445561407</v>
+        <v>51.44725084171054</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08953330117379696</v>
+        <v>0.08929812789059247</v>
       </c>
       <c r="C6">
-        <v>7379.132965778528</v>
+        <v>7328.814890409362</v>
       </c>
       <c r="D6">
-        <v>7448.088965778528</v>
+        <v>7473.684890409362</v>
       </c>
       <c r="E6">
-        <v>244.756</v>
+        <v>320.67</v>
       </c>
       <c r="F6">
-        <v>303.656</v>
+        <v>379.57</v>
       </c>
       <c r="G6">
         <v>234.7</v>
@@ -1910,28 +1910,28 @@
         <v>785.8</v>
       </c>
       <c r="M6">
-        <v>15.2738968</v>
+        <v>19.092371</v>
       </c>
       <c r="N6">
-        <v>770.5261032</v>
+        <v>766.707629</v>
       </c>
       <c r="O6">
-        <v>227.305200444</v>
+        <v>226.178750555</v>
       </c>
       <c r="P6">
-        <v>543.220902756</v>
+        <v>540.528878445</v>
       </c>
       <c r="Q6">
-        <v>645.720902756</v>
+        <v>643.028878445</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09178629288937185</v>
+        <v>0.09213163462167628</v>
       </c>
       <c r="T6">
-        <v>0.7113933256048848</v>
+        <v>0.7167356523718024</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.44725084171054</v>
+        <v>41.15780067336843</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08929812789059247</v>
+        <v>0.08906295460738795</v>
       </c>
       <c r="C7">
-        <v>7328.814890409362</v>
+        <v>7278.673346389996</v>
       </c>
       <c r="D7">
-        <v>7473.684890409362</v>
+        <v>7499.457346389997</v>
       </c>
       <c r="E7">
-        <v>320.67</v>
+        <v>396.5840000000001</v>
       </c>
       <c r="F7">
-        <v>379.57</v>
+        <v>455.484</v>
       </c>
       <c r="G7">
         <v>234.7</v>
@@ -1992,28 +1992,28 @@
         <v>785.8</v>
       </c>
       <c r="M7">
-        <v>19.092371</v>
+        <v>22.9108452</v>
       </c>
       <c r="N7">
-        <v>766.707629</v>
+        <v>762.8891547999999</v>
       </c>
       <c r="O7">
-        <v>226.178750555</v>
+        <v>225.052300666</v>
       </c>
       <c r="P7">
-        <v>540.528878445</v>
+        <v>537.836854134</v>
       </c>
       <c r="Q7">
-        <v>643.028878445</v>
+        <v>640.336854134</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09213163462167628</v>
+        <v>0.09248432405041271</v>
       </c>
       <c r="T7">
-        <v>0.7167356523718024</v>
+        <v>0.7221916456656754</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.15780067336843</v>
+        <v>34.29816722780703</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08906295460738795</v>
+        <v>0.08882778132418344</v>
       </c>
       <c r="C8">
-        <v>7278.673346389996</v>
+        <v>7228.710166306328</v>
       </c>
       <c r="D8">
-        <v>7499.457346389997</v>
+        <v>7525.408166306328</v>
       </c>
       <c r="E8">
-        <v>396.584</v>
+        <v>472.4979999999999</v>
       </c>
       <c r="F8">
-        <v>455.484</v>
+        <v>531.3979999999999</v>
       </c>
       <c r="G8">
         <v>234.7</v>
@@ -2074,28 +2074,28 @@
         <v>785.8</v>
       </c>
       <c r="M8">
-        <v>22.9108452</v>
+        <v>26.72931939999999</v>
       </c>
       <c r="N8">
-        <v>762.8891547999999</v>
+        <v>759.0706805999999</v>
       </c>
       <c r="O8">
-        <v>225.052300666</v>
+        <v>223.925850777</v>
       </c>
       <c r="P8">
-        <v>537.836854134</v>
+        <v>535.144829823</v>
       </c>
       <c r="Q8">
-        <v>640.336854134</v>
+        <v>637.644829823</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09248432405041271</v>
+        <v>0.0928445981980467</v>
       </c>
       <c r="T8">
-        <v>0.7221916456656754</v>
+        <v>0.7277649721486641</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.29816722780703</v>
+        <v>29.39842905240603</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08882778132418344</v>
+        <v>0.08859260804097893</v>
       </c>
       <c r="C9">
-        <v>7228.710166306328</v>
+        <v>7178.927208197967</v>
       </c>
       <c r="D9">
-        <v>7525.408166306328</v>
+        <v>7551.539208197967</v>
       </c>
       <c r="E9">
-        <v>472.498</v>
+        <v>548.412</v>
       </c>
       <c r="F9">
-        <v>531.398</v>
+        <v>607.312</v>
       </c>
       <c r="G9">
         <v>234.7</v>
@@ -2156,28 +2156,28 @@
         <v>785.8</v>
       </c>
       <c r="M9">
-        <v>26.7293194</v>
+        <v>30.5477936</v>
       </c>
       <c r="N9">
-        <v>759.0706805999999</v>
+        <v>755.2522064</v>
       </c>
       <c r="O9">
-        <v>223.925850777</v>
+        <v>222.799400888</v>
       </c>
       <c r="P9">
-        <v>535.144829823</v>
+        <v>532.4528055119999</v>
       </c>
       <c r="Q9">
-        <v>637.644829823</v>
+        <v>634.9528055119999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0928445981980467</v>
+        <v>0.0932127043923684</v>
       </c>
       <c r="T9">
-        <v>0.7277649721486641</v>
+        <v>0.7334594579030221</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.39842905240602</v>
+        <v>25.72362542085527</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08859260804097893</v>
+        <v>0.08835743475777441</v>
       </c>
       <c r="C10">
-        <v>7178.927208197967</v>
+        <v>7129.326356001686</v>
       </c>
       <c r="D10">
-        <v>7551.539208197967</v>
+        <v>7577.852356001686</v>
       </c>
       <c r="E10">
-        <v>548.412</v>
+        <v>624.3259999999999</v>
       </c>
       <c r="F10">
-        <v>607.312</v>
+        <v>683.2259999999999</v>
       </c>
       <c r="G10">
         <v>234.7</v>
@@ -2238,28 +2238,28 @@
         <v>785.8</v>
       </c>
       <c r="M10">
-        <v>30.5477936</v>
+        <v>34.3662678</v>
       </c>
       <c r="N10">
-        <v>755.2522064</v>
+        <v>751.4337322</v>
       </c>
       <c r="O10">
-        <v>222.799400888</v>
+        <v>221.672950999</v>
       </c>
       <c r="P10">
-        <v>532.4528055119999</v>
+        <v>529.760781201</v>
       </c>
       <c r="Q10">
-        <v>634.9528055119999</v>
+        <v>632.260781201</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0932127043923684</v>
+        <v>0.09358890083271913</v>
       </c>
       <c r="T10">
-        <v>0.7334594579030221</v>
+        <v>0.739279097190443</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.72362542085527</v>
+        <v>22.86544481853802</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08835743475777441</v>
+        <v>0.08812226147456989</v>
       </c>
       <c r="C11">
-        <v>7129.326356001686</v>
+        <v>7079.909520004197</v>
       </c>
       <c r="D11">
-        <v>7577.852356001686</v>
+        <v>7604.349520004197</v>
       </c>
       <c r="E11">
-        <v>624.3259999999999</v>
+        <v>700.2399999999999</v>
       </c>
       <c r="F11">
-        <v>683.2259999999999</v>
+        <v>759.1399999999999</v>
       </c>
       <c r="G11">
         <v>234.7</v>
@@ -2320,28 +2320,28 @@
         <v>785.8</v>
       </c>
       <c r="M11">
-        <v>34.3662678</v>
+        <v>38.18474199999999</v>
       </c>
       <c r="N11">
-        <v>751.4337322</v>
+        <v>747.6152579999999</v>
       </c>
       <c r="O11">
-        <v>221.672950999</v>
+        <v>220.54650111</v>
       </c>
       <c r="P11">
-        <v>529.760781201</v>
+        <v>527.0687568899999</v>
       </c>
       <c r="Q11">
-        <v>632.260781201</v>
+        <v>629.5687568899999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09358890083271913</v>
+        <v>0.09397345719396655</v>
       </c>
       <c r="T11">
-        <v>0.739279097190443</v>
+        <v>0.7452280617953621</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.86544481853802</v>
+        <v>20.57890033668422</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08812226147456989</v>
+        <v>0.08788708819136538</v>
       </c>
       <c r="C12">
-        <v>7079.909520004197</v>
+        <v>7030.678637304446</v>
       </c>
       <c r="D12">
-        <v>7604.349520004197</v>
+        <v>7631.032637304446</v>
       </c>
       <c r="E12">
-        <v>700.24</v>
+        <v>776.154</v>
       </c>
       <c r="F12">
-        <v>759.14</v>
+        <v>835.054</v>
       </c>
       <c r="G12">
         <v>234.7</v>
@@ -2402,28 +2402,28 @@
         <v>785.8</v>
       </c>
       <c r="M12">
-        <v>38.184742</v>
+        <v>42.0032162</v>
       </c>
       <c r="N12">
-        <v>747.6152579999999</v>
+        <v>743.7967838</v>
       </c>
       <c r="O12">
-        <v>220.54650111</v>
+        <v>219.420051221</v>
       </c>
       <c r="P12">
-        <v>527.0687568899999</v>
+        <v>524.376732579</v>
       </c>
       <c r="Q12">
-        <v>629.5687568899999</v>
+        <v>626.876732579</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09397345719396655</v>
+        <v>0.09436665527119706</v>
       </c>
       <c r="T12">
-        <v>0.7452280617953621</v>
+        <v>0.7513107109981445</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.57890033668422</v>
+        <v>18.70809121516747</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08788708819136538</v>
+        <v>0.08765191490816086</v>
       </c>
       <c r="C13">
-        <v>7030.678637304446</v>
+        <v>6981.635672285688</v>
       </c>
       <c r="D13">
-        <v>7631.032637304446</v>
+        <v>7657.903672285688</v>
       </c>
       <c r="E13">
-        <v>776.154</v>
+        <v>852.068</v>
       </c>
       <c r="F13">
-        <v>835.054</v>
+        <v>910.968</v>
       </c>
       <c r="G13">
         <v>234.7</v>
@@ -2484,28 +2484,28 @@
         <v>785.8</v>
       </c>
       <c r="M13">
-        <v>42.0032162</v>
+        <v>45.82169039999999</v>
       </c>
       <c r="N13">
-        <v>743.7967838</v>
+        <v>739.9783096</v>
       </c>
       <c r="O13">
-        <v>219.420051221</v>
+        <v>218.293601332</v>
       </c>
       <c r="P13">
-        <v>524.376732579</v>
+        <v>521.684708268</v>
       </c>
       <c r="Q13">
-        <v>626.876732579</v>
+        <v>624.184708268</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09436665527119706</v>
+        <v>0.09476878966836462</v>
       </c>
       <c r="T13">
-        <v>0.7513107109981445</v>
+        <v>0.7575316022282629</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.70809121516747</v>
+        <v>17.14908361390352</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08765191490816086</v>
+        <v>0.08741674162495636</v>
       </c>
       <c r="C14">
-        <v>6981.635672285688</v>
+        <v>6932.782617097551</v>
       </c>
       <c r="D14">
-        <v>7657.903672285688</v>
+        <v>7684.964617097551</v>
       </c>
       <c r="E14">
-        <v>852.068</v>
+        <v>927.982</v>
       </c>
       <c r="F14">
-        <v>910.968</v>
+        <v>986.8819999999999</v>
       </c>
       <c r="G14">
         <v>234.7</v>
@@ -2566,28 +2566,28 @@
         <v>785.8</v>
       </c>
       <c r="M14">
-        <v>45.82169039999999</v>
+        <v>49.64016459999999</v>
       </c>
       <c r="N14">
-        <v>739.9783096</v>
+        <v>736.1598354</v>
       </c>
       <c r="O14">
-        <v>218.293601332</v>
+        <v>217.167151443</v>
       </c>
       <c r="P14">
-        <v>521.684708268</v>
+        <v>518.9926839570001</v>
       </c>
       <c r="Q14">
-        <v>624.184708268</v>
+        <v>621.4926839570001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09476878966836462</v>
+        <v>0.09518016853443259</v>
       </c>
       <c r="T14">
-        <v>0.7575316022282629</v>
+        <v>0.7638955024521772</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.14908361390352</v>
+        <v>15.82992333591094</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08741674162495636</v>
+        <v>0.08718156834175184</v>
       </c>
       <c r="C15">
-        <v>6932.782617097551</v>
+        <v>6884.121492148383</v>
       </c>
       <c r="D15">
-        <v>7684.964617097551</v>
+        <v>7712.217492148384</v>
       </c>
       <c r="E15">
-        <v>927.982</v>
+        <v>1003.896</v>
       </c>
       <c r="F15">
-        <v>986.8819999999999</v>
+        <v>1062.796</v>
       </c>
       <c r="G15">
         <v>234.7</v>
@@ -2648,28 +2648,28 @@
         <v>785.8</v>
       </c>
       <c r="M15">
-        <v>49.64016459999999</v>
+        <v>53.4586388</v>
       </c>
       <c r="N15">
-        <v>736.1598354</v>
+        <v>732.3413611999999</v>
       </c>
       <c r="O15">
-        <v>217.167151443</v>
+        <v>216.040701554</v>
       </c>
       <c r="P15">
-        <v>518.9926839570001</v>
+        <v>516.300659646</v>
       </c>
       <c r="Q15">
-        <v>621.4926839570001</v>
+        <v>618.800659646</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09518016853443259</v>
+        <v>0.09560111435087423</v>
       </c>
       <c r="T15">
-        <v>0.7638955024521772</v>
+        <v>0.7704074003557172</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.82992333591094</v>
+        <v>14.69921452620301</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08718156834175184</v>
+        <v>0.08694639505854732</v>
       </c>
       <c r="C16">
-        <v>6884.121492148383</v>
+        <v>6835.654346608093</v>
       </c>
       <c r="D16">
-        <v>7712.217492148384</v>
+        <v>7739.664346608093</v>
       </c>
       <c r="E16">
-        <v>1003.896</v>
+        <v>1079.81</v>
       </c>
       <c r="F16">
-        <v>1062.796</v>
+        <v>1138.71</v>
       </c>
       <c r="G16">
         <v>234.7</v>
@@ -2730,28 +2730,28 @@
         <v>785.8</v>
       </c>
       <c r="M16">
-        <v>53.4586388</v>
+        <v>57.277113</v>
       </c>
       <c r="N16">
-        <v>732.3413611999999</v>
+        <v>728.522887</v>
       </c>
       <c r="O16">
-        <v>216.040701554</v>
+        <v>214.914251665</v>
       </c>
       <c r="P16">
-        <v>516.300659646</v>
+        <v>513.608635335</v>
       </c>
       <c r="Q16">
-        <v>618.800659646</v>
+        <v>616.108635335</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09560111435087423</v>
+        <v>0.09603196477476156</v>
       </c>
       <c r="T16">
-        <v>0.7704074003557172</v>
+        <v>0.7770725193863995</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.69921452620301</v>
+        <v>13.71926689112281</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08694639505854732</v>
+        <v>0.08671122177534279</v>
       </c>
       <c r="C17">
-        <v>6835.654346608093</v>
+        <v>6787.383258921773</v>
       </c>
       <c r="D17">
-        <v>7739.664346608093</v>
+        <v>7767.307258921773</v>
       </c>
       <c r="E17">
-        <v>1079.81</v>
+        <v>1155.724</v>
       </c>
       <c r="F17">
-        <v>1138.71</v>
+        <v>1214.624</v>
       </c>
       <c r="G17">
         <v>234.7</v>
@@ -2812,28 +2812,28 @@
         <v>785.8</v>
       </c>
       <c r="M17">
-        <v>57.27711299999999</v>
+        <v>61.0955872</v>
       </c>
       <c r="N17">
-        <v>728.522887</v>
+        <v>724.7044128</v>
       </c>
       <c r="O17">
-        <v>214.914251665</v>
+        <v>213.787801776</v>
       </c>
       <c r="P17">
-        <v>513.608635335</v>
+        <v>510.916611024</v>
       </c>
       <c r="Q17">
-        <v>616.108635335</v>
+        <v>613.4166110240001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09603196477476156</v>
+        <v>0.09647307354207477</v>
       </c>
       <c r="T17">
-        <v>0.7770725193863995</v>
+        <v>0.7838963317273361</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.71926689112281</v>
+        <v>12.86181271042764</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08671122177534279</v>
+        <v>0.08647604849213829</v>
       </c>
       <c r="C18">
-        <v>6787.383258921773</v>
+        <v>6739.310337334362</v>
       </c>
       <c r="D18">
-        <v>7767.307258921773</v>
+        <v>7795.148337334363</v>
       </c>
       <c r="E18">
-        <v>1155.724</v>
+        <v>1231.638</v>
       </c>
       <c r="F18">
-        <v>1214.624</v>
+        <v>1290.538</v>
       </c>
       <c r="G18">
         <v>234.7</v>
@@ -2894,28 +2894,28 @@
         <v>785.8</v>
       </c>
       <c r="M18">
-        <v>61.0955872</v>
+        <v>64.91406139999999</v>
       </c>
       <c r="N18">
-        <v>724.7044128</v>
+        <v>720.8859385999999</v>
       </c>
       <c r="O18">
-        <v>213.787801776</v>
+        <v>212.661351887</v>
       </c>
       <c r="P18">
-        <v>510.916611024</v>
+        <v>508.224586713</v>
       </c>
       <c r="Q18">
-        <v>613.4166110240001</v>
+        <v>610.724586713</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09647307354207477</v>
+        <v>0.0969248114363112</v>
       </c>
       <c r="T18">
-        <v>0.7838963317273361</v>
+        <v>0.7908845732813072</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.86181271042764</v>
+        <v>12.10523549216719</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08647604849213829</v>
+        <v>0.08624087520893378</v>
       </c>
       <c r="C19">
-        <v>6739.310337334362</v>
+        <v>6691.437720426654</v>
       </c>
       <c r="D19">
-        <v>7795.148337334363</v>
+        <v>7823.189720426654</v>
       </c>
       <c r="E19">
-        <v>1231.638</v>
+        <v>1307.552</v>
       </c>
       <c r="F19">
-        <v>1290.538</v>
+        <v>1366.452</v>
       </c>
       <c r="G19">
         <v>234.7</v>
@@ -2976,28 +2976,28 @@
         <v>785.8</v>
       </c>
       <c r="M19">
-        <v>64.91406139999999</v>
+        <v>68.73253559999999</v>
       </c>
       <c r="N19">
-        <v>720.8859385999999</v>
+        <v>717.0674643999999</v>
       </c>
       <c r="O19">
-        <v>212.661351887</v>
+        <v>211.534901998</v>
       </c>
       <c r="P19">
-        <v>508.224586713</v>
+        <v>505.5325624019999</v>
       </c>
       <c r="Q19">
-        <v>610.724586713</v>
+        <v>608.0325624019999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0969248114363112</v>
+        <v>0.09738756732796802</v>
       </c>
       <c r="T19">
-        <v>0.7908845732813072</v>
+        <v>0.7980432597512289</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.10523549216719</v>
+        <v>11.43272240926901</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0862408752089338</v>
+        <v>0.08600570192572926</v>
       </c>
       <c r="C20">
-        <v>6691.437720426653</v>
+        <v>6643.767577662888</v>
       </c>
       <c r="D20">
-        <v>7823.189720426652</v>
+        <v>7851.433577662889</v>
       </c>
       <c r="E20">
-        <v>1307.552</v>
+        <v>1383.466</v>
       </c>
       <c r="F20">
-        <v>1366.452</v>
+        <v>1442.366</v>
       </c>
       <c r="G20">
         <v>234.7</v>
@@ -3058,28 +3058,28 @@
         <v>785.8</v>
       </c>
       <c r="M20">
-        <v>68.73253559999999</v>
+        <v>72.55100979999999</v>
       </c>
       <c r="N20">
-        <v>717.0674643999999</v>
+        <v>713.2489902</v>
       </c>
       <c r="O20">
-        <v>211.534901998</v>
+        <v>210.408452109</v>
       </c>
       <c r="P20">
-        <v>505.5325624019999</v>
+        <v>502.840538091</v>
       </c>
       <c r="Q20">
-        <v>608.0325624019999</v>
+        <v>605.340538091</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09738756732796802</v>
+        <v>0.09786174929102379</v>
       </c>
       <c r="T20">
-        <v>0.7980432597512289</v>
+        <v>0.805378703911766</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.43272240926901</v>
+        <v>10.83100017720222</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08600570192572926</v>
+        <v>0.08577052864252475</v>
       </c>
       <c r="C21">
-        <v>6643.767577662888</v>
+        <v>6596.302109950258</v>
       </c>
       <c r="D21">
-        <v>7851.433577662889</v>
+        <v>7879.882109950258</v>
       </c>
       <c r="E21">
-        <v>1383.466</v>
+        <v>1459.38</v>
       </c>
       <c r="F21">
-        <v>1442.366</v>
+        <v>1518.28</v>
       </c>
       <c r="G21">
         <v>234.7</v>
@@ -3140,28 +3140,28 @@
         <v>785.8</v>
       </c>
       <c r="M21">
-        <v>72.55100979999999</v>
+        <v>76.369484</v>
       </c>
       <c r="N21">
-        <v>713.2489902</v>
+        <v>709.4305159999999</v>
       </c>
       <c r="O21">
-        <v>210.408452109</v>
+        <v>209.28200222</v>
       </c>
       <c r="P21">
-        <v>502.840538091</v>
+        <v>500.1485137799999</v>
       </c>
       <c r="Q21">
-        <v>605.340538091</v>
+        <v>602.6485137799999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09786174929102379</v>
+        <v>0.09834778580315594</v>
       </c>
       <c r="T21">
-        <v>0.805378703911766</v>
+        <v>0.8128975341763165</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.83100017720222</v>
+        <v>10.28945016834211</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08577052864252475</v>
+        <v>0.08553535535932025</v>
       </c>
       <c r="C22">
-        <v>6596.302109950258</v>
+        <v>6549.043550210637</v>
       </c>
       <c r="D22">
-        <v>7879.882109950258</v>
+        <v>7908.537550210637</v>
       </c>
       <c r="E22">
-        <v>1459.38</v>
+        <v>1535.294</v>
       </c>
       <c r="F22">
-        <v>1518.28</v>
+        <v>1594.194</v>
       </c>
       <c r="G22">
         <v>234.7</v>
@@ -3222,28 +3222,28 @@
         <v>785.8</v>
       </c>
       <c r="M22">
-        <v>76.369484</v>
+        <v>80.18795820000001</v>
       </c>
       <c r="N22">
-        <v>709.4305159999999</v>
+        <v>705.6120417999999</v>
       </c>
       <c r="O22">
-        <v>209.28200222</v>
+        <v>208.155552331</v>
       </c>
       <c r="P22">
-        <v>500.1485137799999</v>
+        <v>497.456489469</v>
       </c>
       <c r="Q22">
-        <v>602.6485137799999</v>
+        <v>599.956489469</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09834778580315594</v>
+        <v>0.09884612703711423</v>
       </c>
       <c r="T22">
-        <v>0.8128975341763165</v>
+        <v>0.8206067145741468</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.28945016834211</v>
+        <v>9.799476350802006</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08553535535932025</v>
+        <v>0.08530018207611573</v>
       </c>
       <c r="C23">
-        <v>6549.043550210637</v>
+        <v>6501.994163964806</v>
       </c>
       <c r="D23">
-        <v>7908.537550210637</v>
+        <v>7937.402163964806</v>
       </c>
       <c r="E23">
-        <v>1535.294</v>
+        <v>1611.208</v>
       </c>
       <c r="F23">
-        <v>1594.194</v>
+        <v>1670.108</v>
       </c>
       <c r="G23">
         <v>234.7</v>
@@ -3304,28 +3304,28 @@
         <v>785.8</v>
       </c>
       <c r="M23">
-        <v>80.1879582</v>
+        <v>84.00643239999999</v>
       </c>
       <c r="N23">
-        <v>705.6120417999999</v>
+        <v>701.7935676</v>
       </c>
       <c r="O23">
-        <v>208.155552331</v>
+        <v>207.029102442</v>
       </c>
       <c r="P23">
-        <v>497.456489469</v>
+        <v>494.764465158</v>
       </c>
       <c r="Q23">
-        <v>599.956489469</v>
+        <v>597.264465158</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09884612703711423</v>
+        <v>0.09935724625143041</v>
       </c>
       <c r="T23">
-        <v>0.8206067145741468</v>
+        <v>0.8285135662642291</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.799476350802008</v>
+        <v>9.354045607583735</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08530018207611573</v>
+        <v>0.08506500879291121</v>
       </c>
       <c r="C24">
-        <v>6501.994163964806</v>
+        <v>6455.156249929535</v>
       </c>
       <c r="D24">
-        <v>7937.402163964806</v>
+        <v>7966.478249929534</v>
       </c>
       <c r="E24">
-        <v>1611.208</v>
+        <v>1687.122</v>
       </c>
       <c r="F24">
-        <v>1670.108</v>
+        <v>1746.022</v>
       </c>
       <c r="G24">
         <v>234.7</v>
@@ -3386,28 +3386,28 @@
         <v>785.8</v>
       </c>
       <c r="M24">
-        <v>84.00643239999999</v>
+        <v>87.82490659999999</v>
       </c>
       <c r="N24">
-        <v>701.7935676</v>
+        <v>697.9750934</v>
       </c>
       <c r="O24">
-        <v>207.029102442</v>
+        <v>205.902652553</v>
       </c>
       <c r="P24">
-        <v>494.764465158</v>
+        <v>492.072440847</v>
       </c>
       <c r="Q24">
-        <v>597.264465158</v>
+        <v>594.5724408470001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09935724625143041</v>
+        <v>0.09988164128949507</v>
       </c>
       <c r="T24">
-        <v>0.8285135662642291</v>
+        <v>0.8366257907254824</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.354045607583735</v>
+        <v>8.9473479724714</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08506500879291121</v>
+        <v>0.0850836355097067</v>
       </c>
       <c r="C25">
-        <v>6455.156249929535</v>
+        <v>6376.931535504527</v>
       </c>
       <c r="D25">
-        <v>7966.478249929534</v>
+        <v>7964.167535504526</v>
       </c>
       <c r="E25">
-        <v>1687.122</v>
+        <v>1763.036</v>
       </c>
       <c r="F25">
-        <v>1746.022</v>
+        <v>1821.936</v>
       </c>
       <c r="G25">
         <v>234.7</v>
@@ -3468,45 +3468,45 @@
         <v>785.8</v>
       </c>
       <c r="M25">
-        <v>87.82490659999999</v>
+        <v>94.37628480000001</v>
       </c>
       <c r="N25">
-        <v>697.9750934</v>
+        <v>691.4237151999999</v>
       </c>
       <c r="O25">
-        <v>205.902652553</v>
+        <v>203.969995984</v>
       </c>
       <c r="P25">
-        <v>492.072440847</v>
+        <v>487.453719216</v>
       </c>
       <c r="Q25">
-        <v>594.5724408470001</v>
+        <v>589.953719216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09988164128949507</v>
+        <v>0.1004198361969825</v>
       </c>
       <c r="T25">
-        <v>0.8366257907254824</v>
+        <v>0.8449514947778213</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.295</v>
       </c>
       <c r="W25">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>8.9473479724714</v>
+        <v>8.326244264279408</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0850836355097067</v>
+        <v>0.08485903722650219</v>
       </c>
       <c r="C26">
-        <v>6376.931535504527</v>
+        <v>6328.969477679988</v>
       </c>
       <c r="D26">
-        <v>7964.167535504526</v>
+        <v>7992.119477679988</v>
       </c>
       <c r="E26">
-        <v>1763.036</v>
+        <v>1838.95</v>
       </c>
       <c r="F26">
-        <v>1821.936</v>
+        <v>1897.85</v>
       </c>
       <c r="G26">
         <v>234.7</v>
@@ -3550,28 +3550,28 @@
         <v>785.8</v>
       </c>
       <c r="M26">
-        <v>94.37628479999999</v>
+        <v>98.30862999999999</v>
       </c>
       <c r="N26">
-        <v>691.4237151999999</v>
+        <v>687.49137</v>
       </c>
       <c r="O26">
-        <v>203.969995984</v>
+        <v>202.80995415</v>
       </c>
       <c r="P26">
-        <v>487.453719216</v>
+        <v>484.68141585</v>
       </c>
       <c r="Q26">
-        <v>589.953719216</v>
+        <v>587.18141585</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1004198361969825</v>
+        <v>0.1009723829686696</v>
       </c>
       <c r="T26">
-        <v>0.8449514947778213</v>
+        <v>0.8534992176048892</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.32624426427941</v>
+        <v>7.993194493708233</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08485903722650219</v>
+        <v>0.08463443894329767</v>
       </c>
       <c r="C27">
-        <v>6328.969477679988</v>
+        <v>6281.204317498213</v>
       </c>
       <c r="D27">
-        <v>7992.119477679988</v>
+        <v>8020.268317498212</v>
       </c>
       <c r="E27">
-        <v>1838.95</v>
+        <v>1914.864</v>
       </c>
       <c r="F27">
-        <v>1897.85</v>
+        <v>1973.764</v>
       </c>
       <c r="G27">
         <v>234.7</v>
@@ -3632,28 +3632,28 @@
         <v>785.8</v>
       </c>
       <c r="M27">
-        <v>98.30862999999999</v>
+        <v>102.2409752</v>
       </c>
       <c r="N27">
-        <v>687.49137</v>
+        <v>683.5590248</v>
       </c>
       <c r="O27">
-        <v>202.80995415</v>
+        <v>201.649912316</v>
       </c>
       <c r="P27">
-        <v>484.68141585</v>
+        <v>481.909112484</v>
       </c>
       <c r="Q27">
-        <v>587.18141585</v>
+        <v>584.4091124839999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1009723829686696</v>
+        <v>0.1015398634368887</v>
       </c>
       <c r="T27">
-        <v>0.8534992176048892</v>
+        <v>0.8622779599678239</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.993194493708233</v>
+        <v>7.685763936257916</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08463443894329767</v>
+        <v>0.08440984066009316</v>
       </c>
       <c r="C28">
-        <v>6281.204317498213</v>
+        <v>6233.638142777114</v>
       </c>
       <c r="D28">
-        <v>8020.268317498212</v>
+        <v>8048.616142777113</v>
       </c>
       <c r="E28">
-        <v>1914.864</v>
+        <v>1990.778</v>
       </c>
       <c r="F28">
-        <v>1973.764</v>
+        <v>2049.678</v>
       </c>
       <c r="G28">
         <v>234.7</v>
@@ -3714,28 +3714,28 @@
         <v>785.8</v>
       </c>
       <c r="M28">
-        <v>102.2409752</v>
+        <v>106.1733204</v>
       </c>
       <c r="N28">
-        <v>683.5590248</v>
+        <v>679.6266796</v>
       </c>
       <c r="O28">
-        <v>201.649912316</v>
+        <v>200.489870482</v>
       </c>
       <c r="P28">
-        <v>481.909112484</v>
+        <v>479.136809118</v>
       </c>
       <c r="Q28">
-        <v>584.4091124839999</v>
+        <v>581.636809118</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1015398634368887</v>
+        <v>0.1021228913151961</v>
       </c>
       <c r="T28">
-        <v>0.8622779599678239</v>
+        <v>0.871297215820154</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.685763936257916</v>
+        <v>7.401106012692808</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08440984066009316</v>
+        <v>0.08418524237688862</v>
       </c>
       <c r="C29">
-        <v>6233.638142777114</v>
+        <v>6186.273070957088</v>
       </c>
       <c r="D29">
-        <v>8048.616142777113</v>
+        <v>8077.165070957089</v>
       </c>
       <c r="E29">
-        <v>1990.778</v>
+        <v>2066.692</v>
       </c>
       <c r="F29">
-        <v>2049.678</v>
+        <v>2125.592</v>
       </c>
       <c r="G29">
         <v>234.7</v>
@@ -3796,28 +3796,28 @@
         <v>785.8</v>
       </c>
       <c r="M29">
-        <v>106.1733204</v>
+        <v>110.1056656</v>
       </c>
       <c r="N29">
-        <v>679.6266796</v>
+        <v>675.6943343999999</v>
       </c>
       <c r="O29">
-        <v>200.489870482</v>
+        <v>199.329828648</v>
       </c>
       <c r="P29">
-        <v>479.136809118</v>
+        <v>476.3645057519999</v>
       </c>
       <c r="Q29">
-        <v>581.636809118</v>
+        <v>578.8645057519999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1021228913151961</v>
+        <v>0.1027221144123453</v>
       </c>
       <c r="T29">
-        <v>0.871297215820154</v>
+        <v>0.8805670065572709</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.401106012692808</v>
+        <v>7.136780797953778</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08418524237688862</v>
+        <v>0.08396064409368413</v>
       </c>
       <c r="C30">
-        <v>6186.273070957088</v>
+        <v>6139.11124962821</v>
       </c>
       <c r="D30">
-        <v>8077.165070957089</v>
+        <v>8105.91724962821</v>
       </c>
       <c r="E30">
-        <v>2066.692</v>
+        <v>2142.606</v>
       </c>
       <c r="F30">
-        <v>2125.592</v>
+        <v>2201.506</v>
       </c>
       <c r="G30">
         <v>234.7</v>
@@ -3878,28 +3878,28 @@
         <v>785.8</v>
       </c>
       <c r="M30">
-        <v>110.1056656</v>
+        <v>114.0380108</v>
       </c>
       <c r="N30">
-        <v>675.6943343999999</v>
+        <v>671.7619891999999</v>
       </c>
       <c r="O30">
-        <v>199.329828648</v>
+        <v>198.169786814</v>
       </c>
       <c r="P30">
-        <v>476.3645057519999</v>
+        <v>473.5922023859999</v>
       </c>
       <c r="Q30">
-        <v>578.8645057519999</v>
+        <v>576.0922023859999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1027221144123453</v>
+        <v>0.1033382170333579</v>
       </c>
       <c r="T30">
-        <v>0.8805670065572709</v>
+        <v>0.8900979181602224</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.136780797953778</v>
+        <v>6.890684908369165</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08396064409368413</v>
+        <v>0.08409559581047961</v>
       </c>
       <c r="C31">
-        <v>6139.111249628211</v>
+        <v>6045.896774067738</v>
       </c>
       <c r="D31">
-        <v>8105.91724962821</v>
+        <v>8088.616774067738</v>
       </c>
       <c r="E31">
-        <v>2142.606</v>
+        <v>2218.52</v>
       </c>
       <c r="F31">
-        <v>2201.506</v>
+        <v>2277.42</v>
       </c>
       <c r="G31">
         <v>234.7</v>
@@ -3960,45 +3960,45 @@
         <v>785.8</v>
       </c>
       <c r="M31">
-        <v>114.0380108</v>
+        <v>121.84197</v>
       </c>
       <c r="N31">
-        <v>671.7619892</v>
+        <v>663.95803</v>
       </c>
       <c r="O31">
-        <v>198.169786814</v>
+        <v>195.86761885</v>
       </c>
       <c r="P31">
-        <v>473.5922023860001</v>
+        <v>468.09041115</v>
       </c>
       <c r="Q31">
-        <v>576.0922023860001</v>
+        <v>570.59041115</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1033382170333579</v>
+        <v>0.1039719225863995</v>
       </c>
       <c r="T31">
-        <v>0.8900979181602224</v>
+        <v>0.8999011415232581</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.295</v>
       </c>
       <c r="W31">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.890684908369167</v>
+        <v>6.449337613303529</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08409559581047961</v>
+        <v>0.08388298252727509</v>
       </c>
       <c r="C32">
-        <v>6045.896774067738</v>
+        <v>5997.272860422604</v>
       </c>
       <c r="D32">
-        <v>8088.616774067738</v>
+        <v>8115.906860422603</v>
       </c>
       <c r="E32">
-        <v>2218.52</v>
+        <v>2294.434</v>
       </c>
       <c r="F32">
-        <v>2277.42</v>
+        <v>2353.334</v>
       </c>
       <c r="G32">
         <v>234.7</v>
@@ -4042,28 +4042,28 @@
         <v>785.8</v>
       </c>
       <c r="M32">
-        <v>121.84197</v>
+        <v>125.903369</v>
       </c>
       <c r="N32">
-        <v>663.95803</v>
+        <v>659.896631</v>
       </c>
       <c r="O32">
-        <v>195.86761885</v>
+        <v>194.669506145</v>
       </c>
       <c r="P32">
-        <v>468.09041115</v>
+        <v>465.2271248549999</v>
       </c>
       <c r="Q32">
-        <v>570.59041115</v>
+        <v>567.7271248549999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1039719225863995</v>
+        <v>0.1046239964163407</v>
       </c>
       <c r="T32">
-        <v>0.8999011415232581</v>
+        <v>0.9099885162881207</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.449337613303529</v>
+        <v>6.241294464487285</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08388298252727509</v>
+        <v>0.08367036924407056</v>
       </c>
       <c r="C33">
-        <v>5997.272860422604</v>
+        <v>5948.833717558291</v>
       </c>
       <c r="D33">
-        <v>8115.906860422603</v>
+        <v>8143.38171755829</v>
       </c>
       <c r="E33">
-        <v>2294.434</v>
+        <v>2370.348</v>
       </c>
       <c r="F33">
-        <v>2353.334</v>
+        <v>2429.248</v>
       </c>
       <c r="G33">
         <v>234.7</v>
@@ -4124,28 +4124,28 @@
         <v>785.8</v>
       </c>
       <c r="M33">
-        <v>125.903369</v>
+        <v>129.964768</v>
       </c>
       <c r="N33">
-        <v>659.896631</v>
+        <v>655.8352319999999</v>
       </c>
       <c r="O33">
-        <v>194.669506145</v>
+        <v>193.47139344</v>
       </c>
       <c r="P33">
-        <v>465.2271248549999</v>
+        <v>462.36383856</v>
       </c>
       <c r="Q33">
-        <v>567.7271248549999</v>
+        <v>564.86383856</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1046239964163407</v>
+        <v>0.1052952488883391</v>
       </c>
       <c r="T33">
-        <v>0.9099885162881207</v>
+        <v>0.9203725785460677</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.241294464487285</v>
+        <v>6.046254012472057</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08367036924407056</v>
+        <v>0.08345775596086605</v>
       </c>
       <c r="C34">
-        <v>5948.833717558291</v>
+        <v>5900.581228367841</v>
       </c>
       <c r="D34">
-        <v>8143.38171755829</v>
+        <v>8171.043228367841</v>
       </c>
       <c r="E34">
-        <v>2370.348</v>
+        <v>2446.262</v>
       </c>
       <c r="F34">
-        <v>2429.248</v>
+        <v>2505.162</v>
       </c>
       <c r="G34">
         <v>234.7</v>
@@ -4206,28 +4206,28 @@
         <v>785.8</v>
       </c>
       <c r="M34">
-        <v>129.964768</v>
+        <v>134.026167</v>
       </c>
       <c r="N34">
-        <v>655.8352319999999</v>
+        <v>651.773833</v>
       </c>
       <c r="O34">
-        <v>193.47139344</v>
+        <v>192.273280735</v>
       </c>
       <c r="P34">
-        <v>462.36383856</v>
+        <v>459.500552265</v>
       </c>
       <c r="Q34">
-        <v>564.86383856</v>
+        <v>562.000552265</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1052952488883391</v>
+        <v>0.1059865387475613</v>
       </c>
       <c r="T34">
-        <v>0.9203725785460677</v>
+        <v>0.9310666128117145</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.046254012472057</v>
+        <v>5.863034193912298</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08345775596086605</v>
+        <v>0.08324514267766155</v>
       </c>
       <c r="C35">
-        <v>5900.581228367841</v>
+        <v>5852.517301414823</v>
       </c>
       <c r="D35">
-        <v>8171.043228367841</v>
+        <v>8198.893301414822</v>
       </c>
       <c r="E35">
-        <v>2446.262</v>
+        <v>2522.176</v>
       </c>
       <c r="F35">
-        <v>2505.162</v>
+        <v>2581.076</v>
       </c>
       <c r="G35">
         <v>234.7</v>
@@ -4288,28 +4288,28 @@
         <v>785.8</v>
       </c>
       <c r="M35">
-        <v>134.026167</v>
+        <v>138.087566</v>
       </c>
       <c r="N35">
-        <v>651.773833</v>
+        <v>647.7124339999999</v>
       </c>
       <c r="O35">
-        <v>192.273280735</v>
+        <v>191.07516803</v>
       </c>
       <c r="P35">
-        <v>459.500552265</v>
+        <v>456.6372659699999</v>
       </c>
       <c r="Q35">
-        <v>562.000552265</v>
+        <v>559.1372659699999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1059865387475613</v>
+        <v>0.1066987767843357</v>
       </c>
       <c r="T35">
-        <v>0.9310666128117145</v>
+        <v>0.9420847087217751</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.863034193912298</v>
+        <v>5.690592011738405</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08324514267766155</v>
+        <v>0.08322992939445704</v>
       </c>
       <c r="C36">
-        <v>5852.517301414823</v>
+        <v>5778.603359235509</v>
       </c>
       <c r="D36">
-        <v>8198.893301414822</v>
+        <v>8200.893359235508</v>
       </c>
       <c r="E36">
-        <v>2522.176</v>
+        <v>2598.09</v>
       </c>
       <c r="F36">
-        <v>2581.076</v>
+        <v>2656.99</v>
       </c>
       <c r="G36">
         <v>234.7</v>
@@ -4370,45 +4370,45 @@
         <v>785.8</v>
       </c>
       <c r="M36">
-        <v>138.087566</v>
+        <v>144.274557</v>
       </c>
       <c r="N36">
-        <v>647.7124339999999</v>
+        <v>641.525443</v>
       </c>
       <c r="O36">
-        <v>191.07516803</v>
+        <v>189.250005685</v>
       </c>
       <c r="P36">
-        <v>456.6372659699999</v>
+        <v>452.275437315</v>
       </c>
       <c r="Q36">
-        <v>559.1372659699999</v>
+        <v>554.775437315</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1066987767843357</v>
+        <v>0.1074329298376262</v>
       </c>
       <c r="T36">
-        <v>0.9420847087217751</v>
+        <v>0.9534418229675297</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.295</v>
       </c>
       <c r="W36">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.690592011738405</v>
+        <v>5.446559783926419</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08322992939445704</v>
+        <v>0.08302295611125252</v>
       </c>
       <c r="C37">
-        <v>5778.603359235509</v>
+        <v>5729.996960035158</v>
       </c>
       <c r="D37">
-        <v>8200.893359235508</v>
+        <v>8228.200960035158</v>
       </c>
       <c r="E37">
-        <v>2598.09</v>
+        <v>2674.004</v>
       </c>
       <c r="F37">
-        <v>2656.99</v>
+        <v>2732.904</v>
       </c>
       <c r="G37">
         <v>234.7</v>
@@ -4452,28 +4452,28 @@
         <v>785.8</v>
       </c>
       <c r="M37">
-        <v>144.274557</v>
+        <v>148.3966872</v>
       </c>
       <c r="N37">
-        <v>641.525443</v>
+        <v>637.4033128</v>
       </c>
       <c r="O37">
-        <v>189.250005685</v>
+        <v>188.033977276</v>
       </c>
       <c r="P37">
-        <v>452.275437315</v>
+        <v>449.369335524</v>
       </c>
       <c r="Q37">
-        <v>554.775437315</v>
+        <v>551.869335524</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1074329298376262</v>
+        <v>0.1081900251738321</v>
       </c>
       <c r="T37">
-        <v>0.9534418229675297</v>
+        <v>0.9651538470334641</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.446559783926419</v>
+        <v>5.29526645659513</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08302295611125252</v>
+        <v>0.082815982828048</v>
       </c>
       <c r="C38">
-        <v>5729.996960035159</v>
+        <v>5681.573027889897</v>
       </c>
       <c r="D38">
-        <v>8228.200960035158</v>
+        <v>8255.691027889896</v>
       </c>
       <c r="E38">
-        <v>2674.003999999999</v>
+        <v>2749.918</v>
       </c>
       <c r="F38">
-        <v>2732.904</v>
+        <v>2808.818</v>
       </c>
       <c r="G38">
         <v>234.7</v>
@@ -4534,28 +4534,28 @@
         <v>785.8</v>
       </c>
       <c r="M38">
-        <v>148.3966872</v>
+        <v>152.5188174</v>
       </c>
       <c r="N38">
-        <v>637.4033128</v>
+        <v>633.2811826</v>
       </c>
       <c r="O38">
-        <v>188.033977276</v>
+        <v>186.817948867</v>
       </c>
       <c r="P38">
-        <v>449.369335524</v>
+        <v>446.463233733</v>
       </c>
       <c r="Q38">
-        <v>551.869335524</v>
+        <v>548.9632337329999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081900251738321</v>
+        <v>0.1089711552826159</v>
       </c>
       <c r="T38">
-        <v>0.965153847033464</v>
+        <v>0.9772376813872058</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.295266456595131</v>
+        <v>5.152151146957425</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.082815982828048</v>
+        <v>0.0826090095448435</v>
       </c>
       <c r="C39">
-        <v>5681.573027889897</v>
+        <v>5633.3333977742</v>
       </c>
       <c r="D39">
-        <v>8255.691027889896</v>
+        <v>8283.3653977742</v>
       </c>
       <c r="E39">
-        <v>2749.918</v>
+        <v>2825.832</v>
       </c>
       <c r="F39">
-        <v>2808.818</v>
+        <v>2884.732</v>
       </c>
       <c r="G39">
         <v>234.7</v>
@@ -4616,28 +4616,28 @@
         <v>785.8</v>
       </c>
       <c r="M39">
-        <v>152.5188174</v>
+        <v>156.6409476</v>
       </c>
       <c r="N39">
-        <v>633.2811826</v>
+        <v>629.1590524</v>
       </c>
       <c r="O39">
-        <v>186.817948867</v>
+        <v>185.601920458</v>
       </c>
       <c r="P39">
-        <v>446.463233733</v>
+        <v>443.557131942</v>
       </c>
       <c r="Q39">
-        <v>548.9632337329999</v>
+        <v>546.057131942</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1089711552826159</v>
+        <v>0.1097774831368444</v>
       </c>
       <c r="T39">
-        <v>0.9772376813872058</v>
+        <v>0.9897113168491329</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.152151146957425</v>
+        <v>5.016568222037492</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0826090095448435</v>
+        <v>0.08240203626163899</v>
       </c>
       <c r="C40">
-        <v>5633.3333977742</v>
+        <v>5585.279929349792</v>
       </c>
       <c r="D40">
-        <v>8283.3653977742</v>
+        <v>8311.225929349792</v>
       </c>
       <c r="E40">
-        <v>2825.832</v>
+        <v>2901.746</v>
       </c>
       <c r="F40">
-        <v>2884.732</v>
+        <v>2960.646</v>
       </c>
       <c r="G40">
         <v>234.7</v>
@@ -4698,28 +4698,28 @@
         <v>785.8</v>
       </c>
       <c r="M40">
-        <v>156.6409476</v>
+        <v>160.7630778</v>
       </c>
       <c r="N40">
-        <v>629.1590524</v>
+        <v>625.0369221999999</v>
       </c>
       <c r="O40">
-        <v>185.601920458</v>
+        <v>184.385892049</v>
       </c>
       <c r="P40">
-        <v>443.557131942</v>
+        <v>440.651030151</v>
       </c>
       <c r="Q40">
-        <v>546.057131942</v>
+        <v>543.151030151</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1097774831368444</v>
+        <v>0.1106102479699</v>
       </c>
       <c r="T40">
-        <v>0.9897113168491329</v>
+        <v>1.00259392396555</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.016568222037492</v>
+        <v>4.887938267626273</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08240203626163899</v>
+        <v>0.08219506297843446</v>
       </c>
       <c r="C41">
-        <v>5585.279929349792</v>
+        <v>5537.414507382206</v>
       </c>
       <c r="D41">
-        <v>8311.225929349792</v>
+        <v>8339.274507382204</v>
       </c>
       <c r="E41">
-        <v>2901.746</v>
+        <v>2977.66</v>
       </c>
       <c r="F41">
-        <v>2960.646</v>
+        <v>3036.56</v>
       </c>
       <c r="G41">
         <v>234.7</v>
@@ -4780,28 +4780,28 @@
         <v>785.8</v>
       </c>
       <c r="M41">
-        <v>160.7630778</v>
+        <v>164.885208</v>
       </c>
       <c r="N41">
-        <v>625.0369221999999</v>
+        <v>620.9147919999999</v>
       </c>
       <c r="O41">
-        <v>184.385892049</v>
+        <v>183.16986364</v>
       </c>
       <c r="P41">
-        <v>440.651030151</v>
+        <v>437.74492836</v>
       </c>
       <c r="Q41">
-        <v>543.151030151</v>
+        <v>540.2449283599999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1106102479699</v>
+        <v>0.1114707716307241</v>
       </c>
       <c r="T41">
-        <v>1.00259392396555</v>
+        <v>1.01590595131918</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.887938267626273</v>
+        <v>4.765739810935617</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08219506297843446</v>
+        <v>0.08198808969522996</v>
       </c>
       <c r="C42">
-        <v>5537.414507382206</v>
+        <v>5489.739042165816</v>
       </c>
       <c r="D42">
-        <v>8339.274507382204</v>
+        <v>8367.513042165816</v>
       </c>
       <c r="E42">
-        <v>2977.66</v>
+        <v>3053.574</v>
       </c>
       <c r="F42">
-        <v>3036.56</v>
+        <v>3112.474</v>
       </c>
       <c r="G42">
         <v>234.7</v>
@@ -4862,28 +4862,28 @@
         <v>785.8</v>
       </c>
       <c r="M42">
-        <v>164.885208</v>
+        <v>169.0073382</v>
       </c>
       <c r="N42">
-        <v>620.9147919999999</v>
+        <v>616.7926617999999</v>
       </c>
       <c r="O42">
-        <v>183.16986364</v>
+        <v>181.953835231</v>
       </c>
       <c r="P42">
-        <v>437.74492836</v>
+        <v>434.8388265689999</v>
       </c>
       <c r="Q42">
-        <v>540.2449283599999</v>
+        <v>537.3388265689999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1114707716307241</v>
+        <v>0.1123604655851355</v>
       </c>
       <c r="T42">
-        <v>1.01590595131918</v>
+        <v>1.02966923383734</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.765739810935617</v>
+        <v>4.649502254571333</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08198808969522996</v>
+        <v>0.08178111641202543</v>
       </c>
       <c r="C43">
-        <v>5489.739042165816</v>
+        <v>5442.255469957559</v>
       </c>
       <c r="D43">
-        <v>8367.513042165816</v>
+        <v>8395.94346995756</v>
       </c>
       <c r="E43">
-        <v>3053.574</v>
+        <v>3129.488</v>
       </c>
       <c r="F43">
-        <v>3112.474</v>
+        <v>3188.388</v>
       </c>
       <c r="G43">
         <v>234.7</v>
@@ -4944,28 +4944,28 @@
         <v>785.8</v>
       </c>
       <c r="M43">
-        <v>169.0073382</v>
+        <v>173.1294684</v>
       </c>
       <c r="N43">
-        <v>616.7926617999999</v>
+        <v>612.6705315999999</v>
       </c>
       <c r="O43">
-        <v>181.953835231</v>
+        <v>180.737806822</v>
       </c>
       <c r="P43">
-        <v>434.8388265689999</v>
+        <v>431.932724778</v>
       </c>
       <c r="Q43">
-        <v>537.3388265689999</v>
+        <v>534.432724778</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1123604655851355</v>
+        <v>0.1132808386414232</v>
       </c>
       <c r="T43">
-        <v>1.02966923383734</v>
+        <v>1.043907112304402</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.649502254571333</v>
+        <v>4.538799819938682</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08178111641202544</v>
+        <v>0.08157414312882091</v>
       </c>
       <c r="C44">
-        <v>5442.255469957558</v>
+        <v>5394.965753419476</v>
       </c>
       <c r="D44">
-        <v>8395.943469957558</v>
+        <v>8424.567753419475</v>
       </c>
       <c r="E44">
-        <v>3129.488</v>
+        <v>3205.402</v>
       </c>
       <c r="F44">
-        <v>3188.388</v>
+        <v>3264.302</v>
       </c>
       <c r="G44">
         <v>234.7</v>
@@ -5026,28 +5026,28 @@
         <v>785.8</v>
       </c>
       <c r="M44">
-        <v>173.1294684</v>
+        <v>177.2515986</v>
       </c>
       <c r="N44">
-        <v>612.6705316</v>
+        <v>608.5484014</v>
       </c>
       <c r="O44">
-        <v>180.737806822</v>
+        <v>179.521778413</v>
       </c>
       <c r="P44">
-        <v>431.932724778</v>
+        <v>429.026622987</v>
       </c>
       <c r="Q44">
-        <v>534.432724778</v>
+        <v>531.526622987</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1132808386414232</v>
+        <v>0.1142335054891595</v>
       </c>
       <c r="T44">
-        <v>1.043907112304402</v>
+        <v>1.05864456545452</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.538799819938683</v>
+        <v>4.433246335754063</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08157414312882091</v>
+        <v>0.08136716984561643</v>
       </c>
       <c r="C45">
-        <v>5394.965753419476</v>
+        <v>5347.871882070378</v>
       </c>
       <c r="D45">
-        <v>8424.567753419475</v>
+        <v>8453.387882070378</v>
       </c>
       <c r="E45">
-        <v>3205.402</v>
+        <v>3281.316</v>
       </c>
       <c r="F45">
-        <v>3264.302</v>
+        <v>3340.216</v>
       </c>
       <c r="G45">
         <v>234.7</v>
@@ -5108,28 +5108,28 @@
         <v>785.8</v>
       </c>
       <c r="M45">
-        <v>177.2515986</v>
+        <v>181.3737288</v>
       </c>
       <c r="N45">
-        <v>608.5484014</v>
+        <v>604.4262712</v>
       </c>
       <c r="O45">
-        <v>179.521778413</v>
+        <v>178.305750004</v>
       </c>
       <c r="P45">
-        <v>429.026622987</v>
+        <v>426.120521196</v>
       </c>
       <c r="Q45">
-        <v>531.526622987</v>
+        <v>528.620521196</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1142335054891595</v>
+        <v>0.1152201961528865</v>
       </c>
       <c r="T45">
-        <v>1.05864456545452</v>
+        <v>1.073908356217141</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.433246335754063</v>
+        <v>4.332490737214197</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08136716984561643</v>
+        <v>0.08147744656241189</v>
       </c>
       <c r="C46">
-        <v>5347.871882070378</v>
+        <v>5256.577831954452</v>
       </c>
       <c r="D46">
-        <v>8453.387882070378</v>
+        <v>8438.007831954452</v>
       </c>
       <c r="E46">
-        <v>3281.316</v>
+        <v>3357.23</v>
       </c>
       <c r="F46">
-        <v>3340.216</v>
+        <v>3416.13</v>
       </c>
       <c r="G46">
         <v>234.7</v>
@@ -5190,45 +5190,45 @@
         <v>785.8</v>
       </c>
       <c r="M46">
-        <v>181.3737288</v>
+        <v>188.911989</v>
       </c>
       <c r="N46">
-        <v>604.4262712</v>
+        <v>596.888011</v>
       </c>
       <c r="O46">
-        <v>178.305750004</v>
+        <v>176.081963245</v>
       </c>
       <c r="P46">
-        <v>426.120521196</v>
+        <v>420.806047755</v>
       </c>
       <c r="Q46">
-        <v>528.620521196</v>
+        <v>523.306047755</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1152201961528865</v>
+        <v>0.1162427664771125</v>
       </c>
       <c r="T46">
-        <v>1.073908356217141</v>
+        <v>1.089727193916584</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.295</v>
       </c>
       <c r="W46">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.332490737214197</v>
+        <v>4.159608948905831</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08147744656241189</v>
+        <v>0.08127752327920738</v>
       </c>
       <c r="C47">
-        <v>5256.577831954452</v>
+        <v>5208.588066720666</v>
       </c>
       <c r="D47">
-        <v>8438.007831954452</v>
+        <v>8465.932066720665</v>
       </c>
       <c r="E47">
-        <v>3357.23</v>
+        <v>3433.144</v>
       </c>
       <c r="F47">
-        <v>3416.13</v>
+        <v>3492.044</v>
       </c>
       <c r="G47">
         <v>234.7</v>
@@ -5272,28 +5272,28 @@
         <v>785.8</v>
       </c>
       <c r="M47">
-        <v>188.911989</v>
+        <v>193.1100332</v>
       </c>
       <c r="N47">
-        <v>596.888011</v>
+        <v>592.6899668</v>
       </c>
       <c r="O47">
-        <v>176.081963245</v>
+        <v>174.843540206</v>
       </c>
       <c r="P47">
-        <v>420.806047755</v>
+        <v>417.846426594</v>
       </c>
       <c r="Q47">
-        <v>523.306047755</v>
+        <v>520.346426594</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1162427664771125</v>
+        <v>0.11730320977631</v>
       </c>
       <c r="T47">
-        <v>1.089727193916584</v>
+        <v>1.106131914493786</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.159608948905831</v>
+        <v>4.069182667407878</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08127752327920738</v>
+        <v>0.08107759999600286</v>
       </c>
       <c r="C48">
-        <v>5208.588066720666</v>
+        <v>5160.783736715501</v>
       </c>
       <c r="D48">
-        <v>8465.932066720665</v>
+        <v>8494.041736715501</v>
       </c>
       <c r="E48">
-        <v>3433.144</v>
+        <v>3509.058</v>
       </c>
       <c r="F48">
-        <v>3492.044</v>
+        <v>3567.958</v>
       </c>
       <c r="G48">
         <v>234.7</v>
@@ -5354,28 +5354,28 @@
         <v>785.8</v>
       </c>
       <c r="M48">
-        <v>193.1100332</v>
+        <v>197.3080774</v>
       </c>
       <c r="N48">
-        <v>592.6899668</v>
+        <v>588.4919226</v>
       </c>
       <c r="O48">
-        <v>174.843540206</v>
+        <v>173.605117167</v>
       </c>
       <c r="P48">
-        <v>417.846426594</v>
+        <v>414.8868054329999</v>
       </c>
       <c r="Q48">
-        <v>520.346426594</v>
+        <v>517.3868054329999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.11730320977631</v>
+        <v>0.118403669803779</v>
       </c>
       <c r="T48">
-        <v>1.106131914493786</v>
+        <v>1.123155681130504</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.069182667407878</v>
+        <v>3.982604312782179</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08107759999600286</v>
+        <v>0.08087767671279836</v>
       </c>
       <c r="C49">
-        <v>5160.783736715501</v>
+        <v>5113.166695209681</v>
       </c>
       <c r="D49">
-        <v>8494.041736715501</v>
+        <v>8522.338695209681</v>
       </c>
       <c r="E49">
-        <v>3509.058</v>
+        <v>3584.972</v>
       </c>
       <c r="F49">
-        <v>3567.958</v>
+        <v>3643.872</v>
       </c>
       <c r="G49">
         <v>234.7</v>
@@ -5436,28 +5436,28 @@
         <v>785.8</v>
       </c>
       <c r="M49">
-        <v>197.3080774</v>
+        <v>201.5061216</v>
       </c>
       <c r="N49">
-        <v>588.4919226</v>
+        <v>584.2938783999999</v>
       </c>
       <c r="O49">
-        <v>173.605117167</v>
+        <v>172.366694128</v>
       </c>
       <c r="P49">
-        <v>414.8868054329999</v>
+        <v>411.927184272</v>
       </c>
       <c r="Q49">
-        <v>517.3868054329999</v>
+        <v>514.427184272</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.118403669803779</v>
+        <v>0.1195464552169199</v>
       </c>
       <c r="T49">
-        <v>1.123155681130504</v>
+        <v>1.14083420802248</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.982604312782179</v>
+        <v>3.899633389599216</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08087767671279836</v>
+        <v>0.08067775342959384</v>
       </c>
       <c r="C50">
-        <v>5113.166695209682</v>
+        <v>5065.738820252347</v>
       </c>
       <c r="D50">
-        <v>8522.338695209681</v>
+        <v>8550.824820252346</v>
       </c>
       <c r="E50">
-        <v>3584.972</v>
+        <v>3660.886</v>
       </c>
       <c r="F50">
-        <v>3643.872</v>
+        <v>3719.786</v>
       </c>
       <c r="G50">
         <v>234.7</v>
@@ -5518,28 +5518,28 @@
         <v>785.8</v>
       </c>
       <c r="M50">
-        <v>201.5061216</v>
+        <v>205.7041658</v>
       </c>
       <c r="N50">
-        <v>584.2938783999999</v>
+        <v>580.0958341999999</v>
       </c>
       <c r="O50">
-        <v>172.366694128</v>
+        <v>171.128271089</v>
       </c>
       <c r="P50">
-        <v>411.927184272</v>
+        <v>408.9675631109999</v>
       </c>
       <c r="Q50">
-        <v>514.427184272</v>
+        <v>511.4675631109999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1195464552169199</v>
+        <v>0.1207340557443016</v>
       </c>
       <c r="T50">
-        <v>1.14083420802248</v>
+        <v>1.159206010478848</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.899633389599217</v>
+        <v>3.820049034709437</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08067775342959384</v>
+        <v>0.08047783014638932</v>
       </c>
       <c r="C51">
-        <v>5065.738820252347</v>
+        <v>5018.502015086547</v>
       </c>
       <c r="D51">
-        <v>8550.824820252346</v>
+        <v>8579.502015086546</v>
       </c>
       <c r="E51">
-        <v>3660.886</v>
+        <v>3736.8</v>
       </c>
       <c r="F51">
-        <v>3719.786</v>
+        <v>3795.7</v>
       </c>
       <c r="G51">
         <v>234.7</v>
@@ -5600,28 +5600,28 @@
         <v>785.8</v>
       </c>
       <c r="M51">
-        <v>205.7041658</v>
+        <v>209.90221</v>
       </c>
       <c r="N51">
-        <v>580.0958341999999</v>
+        <v>575.89779</v>
       </c>
       <c r="O51">
-        <v>171.128271089</v>
+        <v>169.88984805</v>
       </c>
       <c r="P51">
-        <v>408.9675631109999</v>
+        <v>406.00794195</v>
       </c>
       <c r="Q51">
-        <v>511.4675631109999</v>
+        <v>508.50794195</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1207340557443016</v>
+        <v>0.1219691602927786</v>
       </c>
       <c r="T51">
-        <v>1.159206010478848</v>
+        <v>1.17831268503347</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.820049034709437</v>
+        <v>3.743648054015248</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08047783014638932</v>
+        <v>0.08027790686318481</v>
       </c>
       <c r="C52">
-        <v>5018.502015086547</v>
+        <v>4971.458208573127</v>
       </c>
       <c r="D52">
-        <v>8579.502015086546</v>
+        <v>8608.372208573126</v>
       </c>
       <c r="E52">
-        <v>3736.8</v>
+        <v>3812.714</v>
       </c>
       <c r="F52">
-        <v>3795.7</v>
+        <v>3871.614</v>
       </c>
       <c r="G52">
         <v>234.7</v>
@@ -5682,28 +5682,28 @@
         <v>785.8</v>
       </c>
       <c r="M52">
-        <v>209.90221</v>
+        <v>214.1002542</v>
       </c>
       <c r="N52">
-        <v>575.89779</v>
+        <v>571.6997458</v>
       </c>
       <c r="O52">
-        <v>169.88984805</v>
+        <v>168.651425011</v>
       </c>
       <c r="P52">
-        <v>406.00794195</v>
+        <v>403.0483207889999</v>
       </c>
       <c r="Q52">
-        <v>508.50794195</v>
+        <v>505.5483207889999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1219691602927786</v>
+        <v>0.1232546772718057</v>
       </c>
       <c r="T52">
-        <v>1.17831268503347</v>
+        <v>1.198199223855628</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.743648054015248</v>
+        <v>3.670243190211028</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08027790686318481</v>
+        <v>0.08007798357998028</v>
       </c>
       <c r="C53">
-        <v>4971.458208573127</v>
+        <v>4924.609355623223</v>
       </c>
       <c r="D53">
-        <v>8608.372208573126</v>
+        <v>8637.437355623222</v>
       </c>
       <c r="E53">
-        <v>3812.714</v>
+        <v>3888.628</v>
       </c>
       <c r="F53">
-        <v>3871.614</v>
+        <v>3947.528</v>
       </c>
       <c r="G53">
         <v>234.7</v>
@@ -5764,28 +5764,28 @@
         <v>785.8</v>
       </c>
       <c r="M53">
-        <v>214.1002542</v>
+        <v>218.2982984</v>
       </c>
       <c r="N53">
-        <v>571.6997458</v>
+        <v>567.5017015999999</v>
       </c>
       <c r="O53">
-        <v>168.651425011</v>
+        <v>167.413001972</v>
       </c>
       <c r="P53">
-        <v>403.0483207889999</v>
+        <v>400.088699628</v>
       </c>
       <c r="Q53">
-        <v>505.5483207889999</v>
+        <v>502.588699628</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1232546772718057</v>
+        <v>0.1245937574582923</v>
       </c>
       <c r="T53">
-        <v>1.198199223855628</v>
+        <v>1.218914368462043</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.670243190211028</v>
+        <v>3.599661590399277</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08007798357998028</v>
+        <v>0.0798780602967758</v>
       </c>
       <c r="C54">
-        <v>4924.609355623223</v>
+        <v>4877.9574376395</v>
       </c>
       <c r="D54">
-        <v>8637.437355623222</v>
+        <v>8666.6994376395</v>
       </c>
       <c r="E54">
-        <v>3888.628</v>
+        <v>3964.542</v>
       </c>
       <c r="F54">
-        <v>3947.528</v>
+        <v>4023.442</v>
       </c>
       <c r="G54">
         <v>234.7</v>
@@ -5846,28 +5846,28 @@
         <v>785.8</v>
       </c>
       <c r="M54">
-        <v>218.2982984</v>
+        <v>222.4963426</v>
       </c>
       <c r="N54">
-        <v>567.5017015999999</v>
+        <v>563.3036573999999</v>
       </c>
       <c r="O54">
-        <v>167.413001972</v>
+        <v>166.174578933</v>
       </c>
       <c r="P54">
-        <v>400.088699628</v>
+        <v>397.1290784669999</v>
       </c>
       <c r="Q54">
-        <v>502.588699628</v>
+        <v>499.6290784669999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1245937574582923</v>
+        <v>0.125989819780374</v>
       </c>
       <c r="T54">
-        <v>1.218914368462043</v>
+        <v>1.240511008583625</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.599661590399277</v>
+        <v>3.531743447184196</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0798780602967758</v>
+        <v>0.07967813701357127</v>
       </c>
       <c r="C55">
-        <v>4877.9574376395</v>
+        <v>4831.504462966468</v>
       </c>
       <c r="D55">
-        <v>8666.6994376395</v>
+        <v>8696.160462966467</v>
       </c>
       <c r="E55">
-        <v>3964.542</v>
+        <v>4040.456</v>
       </c>
       <c r="F55">
-        <v>4023.442</v>
+        <v>4099.356</v>
       </c>
       <c r="G55">
         <v>234.7</v>
@@ -5928,28 +5928,28 @@
         <v>785.8</v>
       </c>
       <c r="M55">
-        <v>222.4963426</v>
+        <v>226.6943868</v>
       </c>
       <c r="N55">
-        <v>563.3036573999999</v>
+        <v>559.1056132</v>
       </c>
       <c r="O55">
-        <v>166.174578933</v>
+        <v>164.936155894</v>
       </c>
       <c r="P55">
-        <v>397.1290784669999</v>
+        <v>394.169457306</v>
       </c>
       <c r="Q55">
-        <v>499.6290784669999</v>
+        <v>496.669457306</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.125989819780374</v>
+        <v>0.1274465804642854</v>
       </c>
       <c r="T55">
-        <v>1.240511008583625</v>
+        <v>1.263046633058318</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.531743447184196</v>
+        <v>3.46634079075486</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07967813701357127</v>
+        <v>0.07947821373036676</v>
       </c>
       <c r="C56">
-        <v>4831.504462966468</v>
+        <v>4785.252467349903</v>
       </c>
       <c r="D56">
-        <v>8696.160462966467</v>
+        <v>8725.822467349903</v>
       </c>
       <c r="E56">
-        <v>4040.456</v>
+        <v>4116.370000000001</v>
       </c>
       <c r="F56">
-        <v>4099.356</v>
+        <v>4175.27</v>
       </c>
       <c r="G56">
         <v>234.7</v>
@@ -6010,28 +6010,28 @@
         <v>785.8</v>
       </c>
       <c r="M56">
-        <v>226.6943868</v>
+        <v>230.892431</v>
       </c>
       <c r="N56">
-        <v>559.1056132</v>
+        <v>554.907569</v>
       </c>
       <c r="O56">
-        <v>164.936155894</v>
+        <v>163.697732855</v>
       </c>
       <c r="P56">
-        <v>394.169457306</v>
+        <v>391.209836145</v>
       </c>
       <c r="Q56">
-        <v>496.669457306</v>
+        <v>493.709836145</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1274465804642854</v>
+        <v>0.1289680860674817</v>
       </c>
       <c r="T56">
-        <v>1.263046633058318</v>
+        <v>1.286583840842998</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.46634079075486</v>
+        <v>3.403316412741134</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07947821373036676</v>
+        <v>0.07927829044716224</v>
       </c>
       <c r="C57">
-        <v>4785.252467349903</v>
+        <v>4739.203514405822</v>
       </c>
       <c r="D57">
-        <v>8725.822467349903</v>
+        <v>8755.687514405821</v>
       </c>
       <c r="E57">
-        <v>4116.370000000001</v>
+        <v>4192.284000000001</v>
       </c>
       <c r="F57">
-        <v>4175.27</v>
+        <v>4251.184</v>
       </c>
       <c r="G57">
         <v>234.7</v>
@@ -6092,28 +6092,28 @@
         <v>785.8</v>
       </c>
       <c r="M57">
-        <v>230.892431</v>
+        <v>235.0904752</v>
       </c>
       <c r="N57">
-        <v>554.907569</v>
+        <v>550.7095247999999</v>
       </c>
       <c r="O57">
-        <v>163.697732855</v>
+        <v>162.459309816</v>
       </c>
       <c r="P57">
-        <v>391.209836145</v>
+        <v>388.250214984</v>
       </c>
       <c r="Q57">
-        <v>493.709836145</v>
+        <v>490.750214984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1289680860674817</v>
+        <v>0.1305587510162778</v>
       </c>
       <c r="T57">
-        <v>1.286583840842998</v>
+        <v>1.311190921708799</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.403316412741134</v>
+        <v>3.342542905370757</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07927829044716224</v>
+        <v>0.07907836716395773</v>
       </c>
       <c r="C58">
-        <v>4739.203514405822</v>
+        <v>4693.359696099029</v>
       </c>
       <c r="D58">
-        <v>8755.687514405821</v>
+        <v>8785.757696099028</v>
       </c>
       <c r="E58">
-        <v>4192.284000000001</v>
+        <v>4268.198</v>
       </c>
       <c r="F58">
-        <v>4251.184</v>
+        <v>4327.098</v>
       </c>
       <c r="G58">
         <v>234.7</v>
@@ -6174,28 +6174,28 @@
         <v>785.8</v>
       </c>
       <c r="M58">
-        <v>235.0904752</v>
+        <v>239.2885194</v>
       </c>
       <c r="N58">
-        <v>550.7095247999999</v>
+        <v>546.5114805999999</v>
       </c>
       <c r="O58">
-        <v>162.459309816</v>
+        <v>161.220886777</v>
       </c>
       <c r="P58">
-        <v>388.250214984</v>
+        <v>385.2905938229999</v>
       </c>
       <c r="Q58">
-        <v>490.750214984</v>
+        <v>487.7905938229999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1305587510162778</v>
+        <v>0.132223400381297</v>
       </c>
       <c r="T58">
-        <v>1.311190921708799</v>
+        <v>1.336942517963708</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.342542905370757</v>
+        <v>3.283901801767761</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07907836716395773</v>
+        <v>0.07887844388075321</v>
       </c>
       <c r="C59">
-        <v>4693.359696099029</v>
+        <v>4647.723133231613</v>
       </c>
       <c r="D59">
-        <v>8785.757696099028</v>
+        <v>8816.035133231613</v>
       </c>
       <c r="E59">
-        <v>4268.198</v>
+        <v>4344.112000000001</v>
       </c>
       <c r="F59">
-        <v>4327.098</v>
+        <v>4403.012000000001</v>
       </c>
       <c r="G59">
         <v>234.7</v>
@@ -6256,28 +6256,28 @@
         <v>785.8</v>
       </c>
       <c r="M59">
-        <v>239.2885194</v>
+        <v>243.4865636</v>
       </c>
       <c r="N59">
-        <v>546.5114805999999</v>
+        <v>542.3134363999999</v>
       </c>
       <c r="O59">
-        <v>161.220886777</v>
+        <v>159.982463738</v>
       </c>
       <c r="P59">
-        <v>385.2905938229999</v>
+        <v>382.3309726619999</v>
       </c>
       <c r="Q59">
-        <v>487.7905938229999</v>
+        <v>484.8309726619999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.132223400381297</v>
+        <v>0.1339673187636981</v>
       </c>
       <c r="T59">
-        <v>1.336942517963708</v>
+        <v>1.363920380706946</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.283901801767761</v>
+        <v>3.227282805185558</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07887844388075321</v>
+        <v>0.07867852059754871</v>
       </c>
       <c r="C60">
-        <v>4647.723133231614</v>
+        <v>4602.295975941552</v>
       </c>
       <c r="D60">
-        <v>8816.035133231613</v>
+        <v>8846.52197594155</v>
       </c>
       <c r="E60">
-        <v>4344.112</v>
+        <v>4420.026</v>
       </c>
       <c r="F60">
-        <v>4403.012</v>
+        <v>4478.925999999999</v>
       </c>
       <c r="G60">
         <v>234.7</v>
@@ -6338,28 +6338,28 @@
         <v>785.8</v>
       </c>
       <c r="M60">
-        <v>243.4865636</v>
+        <v>247.6846078</v>
       </c>
       <c r="N60">
-        <v>542.3134364</v>
+        <v>538.1153922</v>
       </c>
       <c r="O60">
-        <v>159.982463738</v>
+        <v>158.744040699</v>
       </c>
       <c r="P60">
-        <v>382.330972662</v>
+        <v>379.371351501</v>
       </c>
       <c r="Q60">
-        <v>484.830972662</v>
+        <v>481.871351501</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1339673187636981</v>
+        <v>0.1357963063354846</v>
       </c>
       <c r="T60">
-        <v>1.363920380706946</v>
+        <v>1.392214236754731</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.227282805185559</v>
+        <v>3.172583096623092</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07867852059754871</v>
+        <v>0.07847859731434419</v>
       </c>
       <c r="C61">
-        <v>4602.295975941552</v>
+        <v>4557.080404211706</v>
       </c>
       <c r="D61">
-        <v>8846.52197594155</v>
+        <v>8877.220404211705</v>
       </c>
       <c r="E61">
-        <v>4420.026</v>
+        <v>4495.94</v>
       </c>
       <c r="F61">
-        <v>4478.925999999999</v>
+        <v>4554.839999999999</v>
       </c>
       <c r="G61">
         <v>234.7</v>
@@ -6420,28 +6420,28 @@
         <v>785.8</v>
       </c>
       <c r="M61">
-        <v>247.6846078</v>
+        <v>251.882652</v>
       </c>
       <c r="N61">
-        <v>538.1153922</v>
+        <v>533.9173479999999</v>
       </c>
       <c r="O61">
-        <v>158.744040699</v>
+        <v>157.50561766</v>
       </c>
       <c r="P61">
-        <v>379.371351501</v>
+        <v>376.41173034</v>
       </c>
       <c r="Q61">
-        <v>481.871351501</v>
+        <v>478.91173034</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1357963063354846</v>
+        <v>0.1377167432858604</v>
       </c>
       <c r="T61">
-        <v>1.392214236754731</v>
+        <v>1.421922785604907</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.172583096623092</v>
+        <v>3.119706711679374</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07847859731434419</v>
+        <v>0.07827867403113967</v>
       </c>
       <c r="C62">
-        <v>4557.080404211706</v>
+        <v>4512.078628389448</v>
       </c>
       <c r="D62">
-        <v>8877.220404211705</v>
+        <v>8908.132628389447</v>
       </c>
       <c r="E62">
-        <v>4495.94</v>
+        <v>4571.854</v>
       </c>
       <c r="F62">
-        <v>4554.839999999999</v>
+        <v>4630.754</v>
       </c>
       <c r="G62">
         <v>234.7</v>
@@ -6502,28 +6502,28 @@
         <v>785.8</v>
       </c>
       <c r="M62">
-        <v>251.882652</v>
+        <v>256.0806962</v>
       </c>
       <c r="N62">
-        <v>533.9173479999999</v>
+        <v>529.7193038</v>
       </c>
       <c r="O62">
-        <v>157.50561766</v>
+        <v>156.267194621</v>
       </c>
       <c r="P62">
-        <v>376.41173034</v>
+        <v>373.452109179</v>
       </c>
       <c r="Q62">
-        <v>478.91173034</v>
+        <v>475.952109179</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1377167432858604</v>
+        <v>0.1397356641824094</v>
       </c>
       <c r="T62">
-        <v>1.421922785604907</v>
+        <v>1.453154849780732</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.119706711679374</v>
+        <v>3.068563978701023</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07827867403113967</v>
+        <v>0.07807875074793516</v>
       </c>
       <c r="C63">
-        <v>4512.078628389448</v>
+        <v>4467.292889717188</v>
       </c>
       <c r="D63">
-        <v>8908.132628389447</v>
+        <v>8939.260889717187</v>
       </c>
       <c r="E63">
-        <v>4571.854</v>
+        <v>4647.768</v>
       </c>
       <c r="F63">
-        <v>4630.754</v>
+        <v>4706.668</v>
       </c>
       <c r="G63">
         <v>234.7</v>
@@ -6584,28 +6584,28 @@
         <v>785.8</v>
       </c>
       <c r="M63">
-        <v>256.0806962</v>
+        <v>260.2787404</v>
       </c>
       <c r="N63">
-        <v>529.7193038</v>
+        <v>525.5212595999999</v>
       </c>
       <c r="O63">
-        <v>156.267194621</v>
+        <v>155.028771582</v>
       </c>
       <c r="P63">
-        <v>373.452109179</v>
+        <v>370.4924880179999</v>
       </c>
       <c r="Q63">
-        <v>475.952109179</v>
+        <v>472.9924880179999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1397356641824094</v>
+        <v>0.1418608440735136</v>
       </c>
       <c r="T63">
-        <v>1.453154849780732</v>
+        <v>1.486030706807916</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.068563978701023</v>
+        <v>3.019071011302619</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07807875074793516</v>
+        <v>0.07898920246473064</v>
       </c>
       <c r="C64">
-        <v>4467.292889717188</v>
+        <v>4251.353536689217</v>
       </c>
       <c r="D64">
-        <v>8939.260889717187</v>
+        <v>8799.235536689215</v>
       </c>
       <c r="E64">
-        <v>4647.768</v>
+        <v>4723.682</v>
       </c>
       <c r="F64">
-        <v>4706.668</v>
+        <v>4782.581999999999</v>
       </c>
       <c r="G64">
         <v>234.7</v>
@@ -6666,45 +6666,45 @@
         <v>785.8</v>
       </c>
       <c r="M64">
-        <v>260.2787404</v>
+        <v>276.4332396</v>
       </c>
       <c r="N64">
-        <v>525.5212595999999</v>
+        <v>509.3667604</v>
       </c>
       <c r="O64">
-        <v>155.028771582</v>
+        <v>150.263194318</v>
       </c>
       <c r="P64">
-        <v>370.4924880179999</v>
+        <v>359.103566082</v>
       </c>
       <c r="Q64">
-        <v>472.9924880179999</v>
+        <v>461.603566082</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1418608440735136</v>
+        <v>0.144100898553326</v>
       </c>
       <c r="T64">
-        <v>1.486030706807916</v>
+        <v>1.520683637187921</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.295</v>
       </c>
       <c r="W64">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.019071011302619</v>
+        <v>2.842639333594816</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07898920246473064</v>
+        <v>0.07880690418152612</v>
       </c>
       <c r="C65">
-        <v>4251.353536689217</v>
+        <v>4203.124243340756</v>
       </c>
       <c r="D65">
-        <v>8799.235536689215</v>
+        <v>8826.920243340755</v>
       </c>
       <c r="E65">
-        <v>4723.682</v>
+        <v>4799.596</v>
       </c>
       <c r="F65">
-        <v>4782.581999999999</v>
+        <v>4858.496</v>
       </c>
       <c r="G65">
         <v>234.7</v>
@@ -6748,28 +6748,28 @@
         <v>785.8</v>
       </c>
       <c r="M65">
-        <v>276.4332396</v>
+        <v>280.8210688</v>
       </c>
       <c r="N65">
-        <v>509.3667604</v>
+        <v>504.9789311999999</v>
       </c>
       <c r="O65">
-        <v>150.263194318</v>
+        <v>148.968784704</v>
       </c>
       <c r="P65">
-        <v>359.103566082</v>
+        <v>356.0101464959999</v>
       </c>
       <c r="Q65">
-        <v>461.603566082</v>
+        <v>458.5101464959999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.144100898553326</v>
+        <v>0.1464654005042392</v>
       </c>
       <c r="T65">
-        <v>1.520683637187921</v>
+        <v>1.557261730366816</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.842639333594816</v>
+        <v>2.798223094007396</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07880690418152612</v>
+        <v>0.07862460589832161</v>
       </c>
       <c r="C66">
-        <v>4203.124243340756</v>
+        <v>4155.069706542703</v>
       </c>
       <c r="D66">
-        <v>8826.920243340755</v>
+        <v>8854.779706542702</v>
       </c>
       <c r="E66">
-        <v>4799.596</v>
+        <v>4875.51</v>
       </c>
       <c r="F66">
-        <v>4858.496</v>
+        <v>4934.41</v>
       </c>
       <c r="G66">
         <v>234.7</v>
@@ -6830,28 +6830,28 @@
         <v>785.8</v>
       </c>
       <c r="M66">
-        <v>280.8210688</v>
+        <v>285.208898</v>
       </c>
       <c r="N66">
-        <v>504.9789311999999</v>
+        <v>500.5911019999999</v>
       </c>
       <c r="O66">
-        <v>148.968784704</v>
+        <v>147.67437509</v>
       </c>
       <c r="P66">
-        <v>356.0101464959999</v>
+        <v>352.91672691</v>
       </c>
       <c r="Q66">
-        <v>458.5101464959999</v>
+        <v>455.41672691</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1464654005042392</v>
+        <v>0.1489650168523474</v>
       </c>
       <c r="T66">
-        <v>1.557261730366816</v>
+        <v>1.59593000029879</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.798223094007396</v>
+        <v>2.755173507945744</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07862460589832161</v>
+        <v>0.0784423076151171</v>
       </c>
       <c r="C67">
-        <v>4155.069706542703</v>
+        <v>4107.191586230295</v>
       </c>
       <c r="D67">
-        <v>8854.779706542702</v>
+        <v>8882.815586230294</v>
       </c>
       <c r="E67">
-        <v>4875.51</v>
+        <v>4951.424</v>
       </c>
       <c r="F67">
-        <v>4934.41</v>
+        <v>5010.324</v>
       </c>
       <c r="G67">
         <v>234.7</v>
@@ -6912,28 +6912,28 @@
         <v>785.8</v>
       </c>
       <c r="M67">
-        <v>285.208898</v>
+        <v>289.5967272</v>
       </c>
       <c r="N67">
-        <v>500.5911019999999</v>
+        <v>496.2032728</v>
       </c>
       <c r="O67">
-        <v>147.67437509</v>
+        <v>146.379965476</v>
       </c>
       <c r="P67">
-        <v>352.91672691</v>
+        <v>349.823307324</v>
       </c>
       <c r="Q67">
-        <v>455.41672691</v>
+        <v>452.323307324</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1489650168523474</v>
+        <v>0.1516116694562268</v>
       </c>
       <c r="T67">
-        <v>1.59593000029879</v>
+        <v>1.636872874344409</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.755173507945744</v>
+        <v>2.713428454795051</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0784423076151171</v>
+        <v>0.07826000933191257</v>
       </c>
       <c r="C68">
-        <v>4107.191586230295</v>
+        <v>4059.4915634282</v>
       </c>
       <c r="D68">
-        <v>8882.815586230294</v>
+        <v>8911.029563428199</v>
       </c>
       <c r="E68">
-        <v>4951.424</v>
+        <v>5027.338000000001</v>
       </c>
       <c r="F68">
-        <v>5010.324</v>
+        <v>5086.238</v>
       </c>
       <c r="G68">
         <v>234.7</v>
@@ -6994,28 +6994,28 @@
         <v>785.8</v>
       </c>
       <c r="M68">
-        <v>289.5967272</v>
+        <v>293.9845564</v>
       </c>
       <c r="N68">
-        <v>496.2032728</v>
+        <v>491.8154435999999</v>
       </c>
       <c r="O68">
-        <v>146.379965476</v>
+        <v>145.085555862</v>
       </c>
       <c r="P68">
-        <v>349.823307324</v>
+        <v>346.7298877379999</v>
       </c>
       <c r="Q68">
-        <v>452.323307324</v>
+        <v>449.2298877379999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1516116694562268</v>
+        <v>0.1544187252482199</v>
       </c>
       <c r="T68">
-        <v>1.636872874344409</v>
+        <v>1.680297134695824</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.713428454795051</v>
+        <v>2.672929522633931</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07826000933191257</v>
+        <v>0.07807771104870806</v>
       </c>
       <c r="C69">
-        <v>4059.4915634282</v>
+        <v>4011.9713405865</v>
       </c>
       <c r="D69">
-        <v>8911.029563428199</v>
+        <v>8939.4233405865</v>
       </c>
       <c r="E69">
-        <v>5027.338000000001</v>
+        <v>5103.252</v>
       </c>
       <c r="F69">
-        <v>5086.238</v>
+        <v>5162.152</v>
       </c>
       <c r="G69">
         <v>234.7</v>
@@ -7076,28 +7076,28 @@
         <v>785.8</v>
       </c>
       <c r="M69">
-        <v>293.9845564</v>
+        <v>298.3723856</v>
       </c>
       <c r="N69">
-        <v>491.8154435999999</v>
+        <v>487.4276143999999</v>
       </c>
       <c r="O69">
-        <v>145.085555862</v>
+        <v>143.791146248</v>
       </c>
       <c r="P69">
-        <v>346.7298877379999</v>
+        <v>343.636468152</v>
       </c>
       <c r="Q69">
-        <v>449.2298877379999</v>
+        <v>446.136468152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1544187252482199</v>
+        <v>0.1574012220272127</v>
       </c>
       <c r="T69">
-        <v>1.680297134695824</v>
+        <v>1.726435411319202</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.672929522633931</v>
+        <v>2.633621735536373</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07807771104870806</v>
+        <v>0.07789541276550355</v>
       </c>
       <c r="C70">
-        <v>4011.9713405865</v>
+        <v>3964.632641923144</v>
       </c>
       <c r="D70">
-        <v>8939.4233405865</v>
+        <v>8967.998641923143</v>
       </c>
       <c r="E70">
-        <v>5103.252</v>
+        <v>5179.166</v>
       </c>
       <c r="F70">
-        <v>5162.152</v>
+        <v>5238.066</v>
       </c>
       <c r="G70">
         <v>234.7</v>
@@ -7158,28 +7158,28 @@
         <v>785.8</v>
       </c>
       <c r="M70">
-        <v>298.3723856</v>
+        <v>302.7602148</v>
       </c>
       <c r="N70">
-        <v>487.4276143999999</v>
+        <v>483.0397851999999</v>
       </c>
       <c r="O70">
-        <v>143.791146248</v>
+        <v>142.496736634</v>
       </c>
       <c r="P70">
-        <v>343.636468152</v>
+        <v>340.5430485659999</v>
       </c>
       <c r="Q70">
-        <v>446.136468152</v>
+        <v>443.0430485659999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1574012220272127</v>
+        <v>0.1605761379532373</v>
       </c>
       <c r="T70">
-        <v>1.726435411319202</v>
+        <v>1.77555035095054</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.633621735536373</v>
+        <v>2.59545330458657</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07789541276550355</v>
+        <v>0.07771311448229903</v>
       </c>
       <c r="C71">
-        <v>3964.632641923144</v>
+        <v>3917.477213772961</v>
       </c>
       <c r="D71">
-        <v>8967.998641923143</v>
+        <v>8996.75721377296</v>
       </c>
       <c r="E71">
-        <v>5179.166</v>
+        <v>5255.080000000001</v>
       </c>
       <c r="F71">
-        <v>5238.066</v>
+        <v>5313.98</v>
       </c>
       <c r="G71">
         <v>234.7</v>
@@ -7240,28 +7240,28 @@
         <v>785.8</v>
       </c>
       <c r="M71">
-        <v>302.7602148</v>
+        <v>307.148044</v>
       </c>
       <c r="N71">
-        <v>483.0397851999999</v>
+        <v>478.6519559999999</v>
       </c>
       <c r="O71">
-        <v>142.496736634</v>
+        <v>141.20232702</v>
       </c>
       <c r="P71">
-        <v>340.5430485659999</v>
+        <v>337.4496289799999</v>
       </c>
       <c r="Q71">
-        <v>443.0430485659999</v>
+        <v>439.9496289799999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1605761379532373</v>
+        <v>0.1639627149409968</v>
       </c>
       <c r="T71">
-        <v>1.77555035095054</v>
+        <v>1.827939619890633</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.59545330458657</v>
+        <v>2.558375400235334</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07771311448229903</v>
+        <v>0.07753081619909453</v>
       </c>
       <c r="C72">
-        <v>3917.477213772961</v>
+        <v>3870.506824943426</v>
       </c>
       <c r="D72">
-        <v>8996.75721377296</v>
+        <v>9025.700824943426</v>
       </c>
       <c r="E72">
-        <v>5255.080000000001</v>
+        <v>5330.994000000001</v>
       </c>
       <c r="F72">
-        <v>5313.98</v>
+        <v>5389.894</v>
       </c>
       <c r="G72">
         <v>234.7</v>
@@ -7322,28 +7322,28 @@
         <v>785.8</v>
       </c>
       <c r="M72">
-        <v>307.148044</v>
+        <v>311.5358732</v>
       </c>
       <c r="N72">
-        <v>478.6519559999999</v>
+        <v>474.2641267999999</v>
       </c>
       <c r="O72">
-        <v>141.20232702</v>
+        <v>139.907917406</v>
       </c>
       <c r="P72">
-        <v>337.4496289799999</v>
+        <v>334.356209394</v>
       </c>
       <c r="Q72">
-        <v>439.9496289799999</v>
+        <v>436.856209394</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1639627149409968</v>
+        <v>0.1675828489623949</v>
       </c>
       <c r="T72">
-        <v>1.827939619890633</v>
+        <v>1.883941941861079</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.558375400235334</v>
+        <v>2.522341943893991</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07753081619909452</v>
+        <v>0.07912511791589001</v>
       </c>
       <c r="C73">
-        <v>3870.506824943429</v>
+        <v>3547.599493416572</v>
       </c>
       <c r="D73">
-        <v>9025.700824943428</v>
+        <v>8778.70749341657</v>
       </c>
       <c r="E73">
-        <v>5330.994</v>
+        <v>5406.907999999999</v>
       </c>
       <c r="F73">
-        <v>5389.893999999999</v>
+        <v>5465.807999999999</v>
       </c>
       <c r="G73">
         <v>234.7</v>
@@ -7404,45 +7404,45 @@
         <v>785.8</v>
       </c>
       <c r="M73">
-        <v>311.5358732</v>
+        <v>335.0540303999999</v>
       </c>
       <c r="N73">
-        <v>474.2641268</v>
+        <v>450.7459696</v>
       </c>
       <c r="O73">
-        <v>139.907917406</v>
+        <v>132.970061032</v>
       </c>
       <c r="P73">
-        <v>334.356209394</v>
+        <v>317.775908568</v>
       </c>
       <c r="Q73">
-        <v>436.856209394</v>
+        <v>420.275908568</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1675828489623949</v>
+        <v>0.1714615639853214</v>
       </c>
       <c r="T73">
-        <v>1.883941941861078</v>
+        <v>1.943944429686555</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.295</v>
       </c>
       <c r="W73">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.522341943893991</v>
+        <v>2.345293381673048</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07912511791589001</v>
+        <v>0.07896749463268549</v>
       </c>
       <c r="C74">
-        <v>3547.599493416572</v>
+        <v>3495.501082173858</v>
       </c>
       <c r="D74">
-        <v>8778.70749341657</v>
+        <v>8802.523082173857</v>
       </c>
       <c r="E74">
-        <v>5406.907999999999</v>
+        <v>5482.822</v>
       </c>
       <c r="F74">
-        <v>5465.807999999999</v>
+        <v>5541.722</v>
       </c>
       <c r="G74">
         <v>234.7</v>
@@ -7486,28 +7486,28 @@
         <v>785.8</v>
       </c>
       <c r="M74">
-        <v>335.0540303999999</v>
+        <v>339.7075586</v>
       </c>
       <c r="N74">
-        <v>450.7459696</v>
+        <v>446.0924414</v>
       </c>
       <c r="O74">
-        <v>132.970061032</v>
+        <v>131.597270213</v>
       </c>
       <c r="P74">
-        <v>317.775908568</v>
+        <v>314.495171187</v>
       </c>
       <c r="Q74">
-        <v>420.275908568</v>
+        <v>416.995171187</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1714615639853214</v>
+        <v>0.1756275912321685</v>
       </c>
       <c r="T74">
-        <v>1.943944429686555</v>
+        <v>2.008391546239845</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.345293381673048</v>
+        <v>2.313166075074786</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07896749463268549</v>
+        <v>0.07880987134948098</v>
       </c>
       <c r="C75">
-        <v>3495.501082173858</v>
+        <v>3443.532240153479</v>
       </c>
       <c r="D75">
-        <v>8802.523082173857</v>
+        <v>8826.468240153477</v>
       </c>
       <c r="E75">
-        <v>5482.822</v>
+        <v>5558.736</v>
       </c>
       <c r="F75">
-        <v>5541.722</v>
+        <v>5617.636</v>
       </c>
       <c r="G75">
         <v>234.7</v>
@@ -7568,28 +7568,28 @@
         <v>785.8</v>
       </c>
       <c r="M75">
-        <v>339.7075586</v>
+        <v>344.3610868</v>
       </c>
       <c r="N75">
-        <v>446.0924414</v>
+        <v>441.4389132</v>
       </c>
       <c r="O75">
-        <v>131.597270213</v>
+        <v>130.224479394</v>
       </c>
       <c r="P75">
-        <v>314.495171187</v>
+        <v>311.214433806</v>
       </c>
       <c r="Q75">
-        <v>416.995171187</v>
+        <v>413.714433806</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1756275912321685</v>
+        <v>0.1801140821133884</v>
       </c>
       <c r="T75">
-        <v>2.008391546239845</v>
+        <v>2.077796133297234</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.313166075074786</v>
+        <v>2.281907074060262</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07880987134948098</v>
+        <v>0.07865224806627646</v>
       </c>
       <c r="C76">
-        <v>3443.532240153479</v>
+        <v>3391.694027625854</v>
       </c>
       <c r="D76">
-        <v>8826.468240153477</v>
+        <v>8850.544027625852</v>
       </c>
       <c r="E76">
-        <v>5558.736</v>
+        <v>5634.65</v>
       </c>
       <c r="F76">
-        <v>5617.636</v>
+        <v>5693.549999999999</v>
       </c>
       <c r="G76">
         <v>234.7</v>
@@ -7650,28 +7650,28 @@
         <v>785.8</v>
       </c>
       <c r="M76">
-        <v>344.3610868</v>
+        <v>349.0146149999999</v>
       </c>
       <c r="N76">
-        <v>441.4389132</v>
+        <v>436.785385</v>
       </c>
       <c r="O76">
-        <v>130.224479394</v>
+        <v>128.851688575</v>
       </c>
       <c r="P76">
-        <v>311.214433806</v>
+        <v>307.933696425</v>
       </c>
       <c r="Q76">
-        <v>413.714433806</v>
+        <v>410.433696425</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1801140821133884</v>
+        <v>0.1849594922651059</v>
       </c>
       <c r="T76">
-        <v>2.077796133297234</v>
+        <v>2.152753087319215</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.281907074060262</v>
+        <v>2.251481646406126</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07865224806627646</v>
+        <v>0.07999486478307195</v>
       </c>
       <c r="C77">
-        <v>3391.694027625854</v>
+        <v>3114.815135003304</v>
       </c>
       <c r="D77">
-        <v>8850.544027625852</v>
+        <v>8649.579135003303</v>
       </c>
       <c r="E77">
-        <v>5634.65</v>
+        <v>5710.564</v>
       </c>
       <c r="F77">
-        <v>5693.549999999999</v>
+        <v>5769.464</v>
       </c>
       <c r="G77">
         <v>234.7</v>
@@ -7732,45 +7732,45 @@
         <v>785.8</v>
       </c>
       <c r="M77">
-        <v>349.0146149999999</v>
+        <v>369.8226424</v>
       </c>
       <c r="N77">
-        <v>436.785385</v>
+        <v>415.9773575999999</v>
       </c>
       <c r="O77">
-        <v>128.851688575</v>
+        <v>122.713320492</v>
       </c>
       <c r="P77">
-        <v>307.933696425</v>
+        <v>293.264037108</v>
       </c>
       <c r="Q77">
-        <v>410.433696425</v>
+        <v>395.764037108</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1849594922651059</v>
+        <v>0.1902086865961331</v>
       </c>
       <c r="T77">
-        <v>2.152753087319215</v>
+        <v>2.23395645417636</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.295</v>
       </c>
       <c r="W77">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.251481646406126</v>
+        <v>2.124802296853634</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07999486478307195</v>
+        <v>0.07985698149986745</v>
       </c>
       <c r="C78">
-        <v>3114.815135003304</v>
+        <v>3059.118226861748</v>
       </c>
       <c r="D78">
-        <v>8649.579135003303</v>
+        <v>8669.796226861747</v>
       </c>
       <c r="E78">
-        <v>5710.564</v>
+        <v>5786.478</v>
       </c>
       <c r="F78">
-        <v>5769.464</v>
+        <v>5845.378</v>
       </c>
       <c r="G78">
         <v>234.7</v>
@@ -7814,28 +7814,28 @@
         <v>785.8</v>
       </c>
       <c r="M78">
-        <v>369.8226424</v>
+        <v>374.6887298</v>
       </c>
       <c r="N78">
-        <v>415.9773575999999</v>
+        <v>411.1112701999999</v>
       </c>
       <c r="O78">
-        <v>122.713320492</v>
+        <v>121.277824709</v>
       </c>
       <c r="P78">
-        <v>293.264037108</v>
+        <v>289.833445491</v>
       </c>
       <c r="Q78">
-        <v>395.764037108</v>
+        <v>392.333445491</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1902086865961331</v>
+        <v>0.1959143326081193</v>
       </c>
       <c r="T78">
-        <v>2.23395645417636</v>
+        <v>2.322220983368909</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.124802296853634</v>
+        <v>2.09720746182956</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07985698149986745</v>
+        <v>0.07971909821666293</v>
       </c>
       <c r="C79">
-        <v>3059.118226861748</v>
+        <v>3003.516048968194</v>
       </c>
       <c r="D79">
-        <v>8669.796226861747</v>
+        <v>8690.108048968194</v>
       </c>
       <c r="E79">
-        <v>5786.478</v>
+        <v>5862.392000000001</v>
       </c>
       <c r="F79">
-        <v>5845.378</v>
+        <v>5921.292</v>
       </c>
       <c r="G79">
         <v>234.7</v>
@@ -7896,28 +7896,28 @@
         <v>785.8</v>
       </c>
       <c r="M79">
-        <v>374.6887298</v>
+        <v>379.5548172000001</v>
       </c>
       <c r="N79">
-        <v>411.1112701999999</v>
+        <v>406.2451827999999</v>
       </c>
       <c r="O79">
-        <v>121.277824709</v>
+        <v>119.842328926</v>
       </c>
       <c r="P79">
-        <v>289.833445491</v>
+        <v>286.4028538739999</v>
       </c>
       <c r="Q79">
-        <v>392.333445491</v>
+        <v>388.9028538739999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1959143326081193</v>
+        <v>0.2021386737121042</v>
       </c>
       <c r="T79">
-        <v>2.322220983368909</v>
+        <v>2.418509560669872</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.09720746182956</v>
+        <v>2.070320186677899</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07971909821666293</v>
+        <v>0.07958121493345841</v>
       </c>
       <c r="C80">
-        <v>3003.516048968194</v>
+        <v>2948.00926869558</v>
       </c>
       <c r="D80">
-        <v>8690.108048968194</v>
+        <v>8710.515268695579</v>
       </c>
       <c r="E80">
-        <v>5862.392000000001</v>
+        <v>5938.306</v>
       </c>
       <c r="F80">
-        <v>5921.292</v>
+        <v>5997.206</v>
       </c>
       <c r="G80">
         <v>234.7</v>
@@ -7978,28 +7978,28 @@
         <v>785.8</v>
       </c>
       <c r="M80">
-        <v>379.5548172000001</v>
+        <v>384.4209046</v>
       </c>
       <c r="N80">
-        <v>406.2451827999999</v>
+        <v>401.3790953999999</v>
       </c>
       <c r="O80">
-        <v>119.842328926</v>
+        <v>118.406833143</v>
       </c>
       <c r="P80">
-        <v>286.4028538739999</v>
+        <v>282.972262257</v>
       </c>
       <c r="Q80">
-        <v>388.9028538739999</v>
+        <v>385.472262257</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2021386737121042</v>
+        <v>0.2089558092069448</v>
       </c>
       <c r="T80">
-        <v>2.418509560669872</v>
+        <v>2.523968478666165</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.070320186677899</v>
+        <v>2.044113602036407</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07958121493345841</v>
+        <v>0.0794433316502539</v>
       </c>
       <c r="C81">
-        <v>2948.00926869558</v>
+        <v>2892.598559700439</v>
       </c>
       <c r="D81">
-        <v>8710.515268695579</v>
+        <v>8731.018559700438</v>
       </c>
       <c r="E81">
-        <v>5938.306</v>
+        <v>6014.22</v>
       </c>
       <c r="F81">
-        <v>5997.206</v>
+        <v>6073.12</v>
       </c>
       <c r="G81">
         <v>234.7</v>
@@ -8060,28 +8060,28 @@
         <v>785.8</v>
       </c>
       <c r="M81">
-        <v>384.4209046</v>
+        <v>389.286992</v>
       </c>
       <c r="N81">
-        <v>401.3790953999999</v>
+        <v>396.513008</v>
       </c>
       <c r="O81">
-        <v>118.406833143</v>
+        <v>116.97133736</v>
       </c>
       <c r="P81">
-        <v>282.972262257</v>
+        <v>279.54167064</v>
       </c>
       <c r="Q81">
-        <v>385.472262257</v>
+        <v>382.04167064</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2089558092069448</v>
+        <v>0.2164546582512695</v>
       </c>
       <c r="T81">
-        <v>2.523968478666165</v>
+        <v>2.639973288462087</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.044113602036407</v>
+        <v>2.018562182010952</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0794433316502539</v>
+        <v>0.08375963836704939</v>
       </c>
       <c r="C82">
-        <v>2892.598559700439</v>
+        <v>2217.489331466247</v>
       </c>
       <c r="D82">
-        <v>8731.018559700438</v>
+        <v>8131.823331466248</v>
       </c>
       <c r="E82">
-        <v>6014.22</v>
+        <v>6090.134000000001</v>
       </c>
       <c r="F82">
-        <v>6073.12</v>
+        <v>6149.034000000001</v>
       </c>
       <c r="G82">
         <v>234.7</v>
@@ -8142,45 +8142,45 @@
         <v>785.8</v>
       </c>
       <c r="M82">
-        <v>389.286992</v>
+        <v>442.1155446000001</v>
       </c>
       <c r="N82">
-        <v>396.513008</v>
+        <v>343.6844553999999</v>
       </c>
       <c r="O82">
-        <v>116.97133736</v>
+        <v>101.386914343</v>
       </c>
       <c r="P82">
-        <v>279.54167064</v>
+        <v>242.2975410569999</v>
       </c>
       <c r="Q82">
-        <v>382.04167064</v>
+        <v>344.7975410569999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2164546582512695</v>
+        <v>0.2247428598265757</v>
       </c>
       <c r="T82">
-        <v>2.639973288462087</v>
+        <v>2.768189130868106</v>
       </c>
       <c r="U82">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V82">
         <v>0.295</v>
       </c>
       <c r="W82">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.018562182010952</v>
+        <v>1.777363428175649</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08375963836704939</v>
+        <v>0.08367674508384487</v>
       </c>
       <c r="C83">
-        <v>2217.489331466247</v>
+        <v>2152.307097203658</v>
       </c>
       <c r="D83">
-        <v>8131.823331466248</v>
+        <v>8142.555097203659</v>
       </c>
       <c r="E83">
-        <v>6090.134000000001</v>
+        <v>6166.048000000001</v>
       </c>
       <c r="F83">
-        <v>6149.034000000001</v>
+        <v>6224.948</v>
       </c>
       <c r="G83">
         <v>234.7</v>
@@ -8224,28 +8224,28 @@
         <v>785.8</v>
       </c>
       <c r="M83">
-        <v>442.1155446000001</v>
+        <v>447.5737612</v>
       </c>
       <c r="N83">
-        <v>343.6844553999999</v>
+        <v>338.2262387999999</v>
       </c>
       <c r="O83">
-        <v>101.386914343</v>
+        <v>99.77674044599998</v>
       </c>
       <c r="P83">
-        <v>242.2975410569999</v>
+        <v>238.449498354</v>
       </c>
       <c r="Q83">
-        <v>344.7975410569999</v>
+        <v>340.949498354</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2247428598265757</v>
+        <v>0.2339519726880271</v>
       </c>
       <c r="T83">
-        <v>2.768189130868106</v>
+        <v>2.910651177985905</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.777363428175649</v>
+        <v>1.755688264417409</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08367674508384487</v>
+        <v>0.08587593680064035</v>
       </c>
       <c r="C84">
-        <v>2152.307097203658</v>
+        <v>1800.943603265531</v>
       </c>
       <c r="D84">
-        <v>8142.555097203659</v>
+        <v>7867.105603265531</v>
       </c>
       <c r="E84">
-        <v>6166.048000000001</v>
+        <v>6241.962</v>
       </c>
       <c r="F84">
-        <v>6224.948</v>
+        <v>6300.862</v>
       </c>
       <c r="G84">
         <v>234.7</v>
@@ -8306,45 +8306,45 @@
         <v>785.8</v>
       </c>
       <c r="M84">
-        <v>447.5737612</v>
+        <v>477.6053396</v>
       </c>
       <c r="N84">
-        <v>338.2262387999999</v>
+        <v>308.1946603999999</v>
       </c>
       <c r="O84">
-        <v>99.77674044599998</v>
+        <v>90.91742481799997</v>
       </c>
       <c r="P84">
-        <v>238.449498354</v>
+        <v>217.2772355819999</v>
       </c>
       <c r="Q84">
-        <v>340.949498354</v>
+        <v>319.7772355819999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2339519726880271</v>
+        <v>0.2442445105920021</v>
       </c>
       <c r="T84">
-        <v>2.910651177985905</v>
+        <v>3.069873465941092</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.295</v>
       </c>
       <c r="W84">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.755688264417409</v>
+        <v>1.645291488277992</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08587593680064035</v>
+        <v>0.08582053851743585</v>
       </c>
       <c r="C85">
-        <v>1800.943603265531</v>
+        <v>1731.739250824029</v>
       </c>
       <c r="D85">
-        <v>7867.105603265531</v>
+        <v>7873.81525082403</v>
       </c>
       <c r="E85">
-        <v>6241.962</v>
+        <v>6317.876000000001</v>
       </c>
       <c r="F85">
-        <v>6300.862</v>
+        <v>6376.776000000001</v>
       </c>
       <c r="G85">
         <v>234.7</v>
@@ -8388,28 +8388,28 @@
         <v>785.8</v>
       </c>
       <c r="M85">
-        <v>477.6053396</v>
+        <v>483.3596208000001</v>
       </c>
       <c r="N85">
-        <v>308.1946603999999</v>
+        <v>302.4403791999999</v>
       </c>
       <c r="O85">
-        <v>90.91742481799997</v>
+        <v>89.21991186399995</v>
       </c>
       <c r="P85">
-        <v>217.2772355819999</v>
+        <v>213.2204673359999</v>
       </c>
       <c r="Q85">
-        <v>319.7772355819999</v>
+        <v>315.720467336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2442445105920021</v>
+        <v>0.2558236157339741</v>
       </c>
       <c r="T85">
-        <v>3.069873465941092</v>
+        <v>3.248998539890679</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.645291488277992</v>
+        <v>1.625704684846111</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08582053851743585</v>
+        <v>0.08576514023423132</v>
       </c>
       <c r="C86">
-        <v>1731.73925082403</v>
+        <v>1662.546353116013</v>
       </c>
       <c r="D86">
-        <v>7873.81525082403</v>
+        <v>7880.536353116013</v>
       </c>
       <c r="E86">
-        <v>6317.876</v>
+        <v>6393.79</v>
       </c>
       <c r="F86">
-        <v>6376.776</v>
+        <v>6452.69</v>
       </c>
       <c r="G86">
         <v>234.7</v>
@@ -8470,28 +8470,28 @@
         <v>785.8</v>
       </c>
       <c r="M86">
-        <v>483.3596208</v>
+        <v>489.113902</v>
       </c>
       <c r="N86">
-        <v>302.4403791999999</v>
+        <v>296.686098</v>
       </c>
       <c r="O86">
-        <v>89.21991186399998</v>
+        <v>87.52239890999998</v>
       </c>
       <c r="P86">
-        <v>213.220467336</v>
+        <v>209.16369909</v>
       </c>
       <c r="Q86">
-        <v>315.720467336</v>
+        <v>311.66369909</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2558236157339739</v>
+        <v>0.2689466015615421</v>
       </c>
       <c r="T86">
-        <v>3.248998539890676</v>
+        <v>3.45200695703354</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.625704684846111</v>
+        <v>1.606578747377334</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08576514023423132</v>
+        <v>0.0857097419510268</v>
       </c>
       <c r="C87">
-        <v>1662.546353116013</v>
+        <v>1593.364939499875</v>
       </c>
       <c r="D87">
-        <v>7880.536353116013</v>
+        <v>7887.268939499874</v>
       </c>
       <c r="E87">
-        <v>6393.79</v>
+        <v>6469.704</v>
       </c>
       <c r="F87">
-        <v>6452.69</v>
+        <v>6528.603999999999</v>
       </c>
       <c r="G87">
         <v>234.7</v>
@@ -8552,28 +8552,28 @@
         <v>785.8</v>
       </c>
       <c r="M87">
-        <v>489.113902</v>
+        <v>494.8681832</v>
       </c>
       <c r="N87">
-        <v>296.686098</v>
+        <v>290.9318168</v>
       </c>
       <c r="O87">
-        <v>87.52239890999998</v>
+        <v>85.82488595599999</v>
       </c>
       <c r="P87">
-        <v>209.16369909</v>
+        <v>205.106930844</v>
       </c>
       <c r="Q87">
-        <v>311.66369909</v>
+        <v>307.606930844</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2689466015615421</v>
+        <v>0.2839442996501914</v>
       </c>
       <c r="T87">
-        <v>3.45200695703354</v>
+        <v>3.684016576625383</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.606578747377334</v>
+        <v>1.587897599152016</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0857097419510268</v>
+        <v>0.08565434366782229</v>
       </c>
       <c r="C88">
-        <v>1593.364939499875</v>
+        <v>1524.195039434431</v>
       </c>
       <c r="D88">
-        <v>7887.268939499874</v>
+        <v>7894.013039434431</v>
       </c>
       <c r="E88">
-        <v>6469.704</v>
+        <v>6545.618</v>
       </c>
       <c r="F88">
-        <v>6528.603999999999</v>
+        <v>6604.518</v>
       </c>
       <c r="G88">
         <v>234.7</v>
@@ -8634,28 +8634,28 @@
         <v>785.8</v>
       </c>
       <c r="M88">
-        <v>494.8681832</v>
+        <v>500.6224644000001</v>
       </c>
       <c r="N88">
-        <v>290.9318168</v>
+        <v>285.1775355999999</v>
       </c>
       <c r="O88">
-        <v>85.82488595599999</v>
+        <v>84.12737300199996</v>
       </c>
       <c r="P88">
-        <v>205.106930844</v>
+        <v>201.0501625979999</v>
       </c>
       <c r="Q88">
-        <v>307.606930844</v>
+        <v>303.5501625979999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2839442996501914</v>
+        <v>0.3012493359063253</v>
       </c>
       <c r="T88">
-        <v>3.684016576625383</v>
+        <v>3.951719983846742</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.587897599152016</v>
+        <v>1.569645902610038</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08565434366782229</v>
+        <v>0.08559894538461779</v>
       </c>
       <c r="C89">
-        <v>1524.195039434431</v>
+        <v>1455.036682479338</v>
       </c>
       <c r="D89">
-        <v>7894.013039434431</v>
+        <v>7900.768682479338</v>
       </c>
       <c r="E89">
-        <v>6545.618</v>
+        <v>6621.532</v>
       </c>
       <c r="F89">
-        <v>6604.518</v>
+        <v>6680.432</v>
       </c>
       <c r="G89">
         <v>234.7</v>
@@ -8716,28 +8716,28 @@
         <v>785.8</v>
       </c>
       <c r="M89">
-        <v>500.6224644000001</v>
+        <v>506.3767456</v>
       </c>
       <c r="N89">
-        <v>285.1775355999999</v>
+        <v>279.4232543999999</v>
       </c>
       <c r="O89">
-        <v>84.12737300199996</v>
+        <v>82.42986004799997</v>
       </c>
       <c r="P89">
-        <v>201.0501625979999</v>
+        <v>196.9933943519999</v>
       </c>
       <c r="Q89">
-        <v>303.5501625979999</v>
+        <v>299.4933943519999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3012493359063253</v>
+        <v>0.3214385448718148</v>
       </c>
       <c r="T89">
-        <v>3.951719983846742</v>
+        <v>4.264040625604993</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.569645902610038</v>
+        <v>1.551809017353106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08559894538461779</v>
+        <v>0.08554354710141326</v>
       </c>
       <c r="C90">
-        <v>1455.036682479338</v>
+        <v>1385.889898295532</v>
       </c>
       <c r="D90">
-        <v>7900.768682479338</v>
+        <v>7907.535898295532</v>
       </c>
       <c r="E90">
-        <v>6621.532</v>
+        <v>6697.446</v>
       </c>
       <c r="F90">
-        <v>6680.432</v>
+        <v>6756.346</v>
       </c>
       <c r="G90">
         <v>234.7</v>
@@ -8798,28 +8798,28 @@
         <v>785.8</v>
       </c>
       <c r="M90">
-        <v>506.3767456</v>
+        <v>512.1310268</v>
       </c>
       <c r="N90">
-        <v>279.4232543999999</v>
+        <v>273.6689732</v>
       </c>
       <c r="O90">
-        <v>82.42986004799997</v>
+        <v>80.73234709399999</v>
       </c>
       <c r="P90">
-        <v>196.9933943519999</v>
+        <v>192.936626106</v>
       </c>
       <c r="Q90">
-        <v>299.4933943519999</v>
+        <v>295.436626106</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3214385448718148</v>
+        <v>0.345298519103757</v>
       </c>
       <c r="T90">
-        <v>4.264040625604993</v>
+        <v>4.633146838592018</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.551809017353106</v>
+        <v>1.534372960978353</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08554354710141326</v>
+        <v>0.08548814881820875</v>
       </c>
       <c r="C91">
-        <v>1385.889898295532</v>
+        <v>1316.754716645647</v>
       </c>
       <c r="D91">
-        <v>7907.535898295532</v>
+        <v>7914.314716645647</v>
       </c>
       <c r="E91">
-        <v>6697.446</v>
+        <v>6773.360000000001</v>
       </c>
       <c r="F91">
-        <v>6756.346</v>
+        <v>6832.26</v>
       </c>
       <c r="G91">
         <v>234.7</v>
@@ -8880,28 +8880,28 @@
         <v>785.8</v>
       </c>
       <c r="M91">
-        <v>512.1310268</v>
+        <v>517.885308</v>
       </c>
       <c r="N91">
-        <v>273.6689732</v>
+        <v>267.9146919999999</v>
       </c>
       <c r="O91">
-        <v>80.73234709399999</v>
+        <v>79.03483413999999</v>
       </c>
       <c r="P91">
-        <v>192.936626106</v>
+        <v>188.87985786</v>
       </c>
       <c r="Q91">
-        <v>295.436626106</v>
+        <v>291.37985786</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.345298519103757</v>
+        <v>0.3739304881820875</v>
       </c>
       <c r="T91">
-        <v>4.633146838592018</v>
+        <v>5.076074294176447</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.534372960978353</v>
+        <v>1.517324372523037</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08548814881820875</v>
+        <v>0.08543275053500424</v>
       </c>
       <c r="C92">
-        <v>1316.754716645647</v>
+        <v>1247.63116739447</v>
       </c>
       <c r="D92">
-        <v>7914.314716645647</v>
+        <v>7921.10516739447</v>
       </c>
       <c r="E92">
-        <v>6773.360000000001</v>
+        <v>6849.274</v>
       </c>
       <c r="F92">
-        <v>6832.26</v>
+        <v>6908.174</v>
       </c>
       <c r="G92">
         <v>234.7</v>
@@ -8962,28 +8962,28 @@
         <v>785.8</v>
       </c>
       <c r="M92">
-        <v>517.885308</v>
+        <v>523.6395892</v>
       </c>
       <c r="N92">
-        <v>267.9146919999999</v>
+        <v>262.1604107999999</v>
       </c>
       <c r="O92">
-        <v>79.03483413999999</v>
+        <v>77.33732118599997</v>
       </c>
       <c r="P92">
-        <v>188.87985786</v>
+        <v>184.8230896139999</v>
       </c>
       <c r="Q92">
-        <v>291.37985786</v>
+        <v>287.323089614</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3739304881820875</v>
+        <v>0.4089251170556027</v>
       </c>
       <c r="T92">
-        <v>5.076074294176447</v>
+        <v>5.617430073224084</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.517324372523037</v>
+        <v>1.500650478319487</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08543275053500424</v>
+        <v>0.09458747225179973</v>
       </c>
       <c r="C93">
-        <v>1247.63116739447</v>
+        <v>188.0796212384348</v>
       </c>
       <c r="D93">
-        <v>7921.10516739447</v>
+        <v>6937.467621238435</v>
       </c>
       <c r="E93">
-        <v>6849.274</v>
+        <v>6925.188</v>
       </c>
       <c r="F93">
-        <v>6908.174</v>
+        <v>6984.088</v>
       </c>
       <c r="G93">
         <v>234.7</v>
@@ -9044,45 +9044,45 @@
         <v>785.8</v>
       </c>
       <c r="M93">
-        <v>523.6395892</v>
+        <v>628.56792</v>
       </c>
       <c r="N93">
-        <v>262.1604107999999</v>
+        <v>157.23208</v>
       </c>
       <c r="O93">
-        <v>77.33732118599997</v>
+        <v>46.3834636</v>
       </c>
       <c r="P93">
-        <v>184.8230896139999</v>
+        <v>110.8486164</v>
       </c>
       <c r="Q93">
-        <v>287.323089614</v>
+        <v>213.3486164</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4089251170556027</v>
+        <v>0.4526684031474967</v>
       </c>
       <c r="T93">
-        <v>5.617430073224084</v>
+        <v>6.294124797033629</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0.295</v>
       </c>
       <c r="W93">
-        <v>0.05343900000000001</v>
+        <v>0.06345000000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.500650478319487</v>
+        <v>1.250143341709198</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09458747225179973</v>
+        <v>0.1161397574042434</v>
       </c>
       <c r="C94">
-        <v>188.0796212384348</v>
+        <v>-1457.183559261845</v>
       </c>
       <c r="D94">
-        <v>6937.467621238435</v>
+        <v>5368.118440738155</v>
       </c>
       <c r="E94">
-        <v>6925.188</v>
+        <v>7001.102000000001</v>
       </c>
       <c r="F94">
-        <v>6984.088</v>
+        <v>7060.002</v>
       </c>
       <c r="G94">
         <v>234.7</v>
@@ -9126,45 +9126,45 @@
         <v>785.8</v>
       </c>
       <c r="M94">
-        <v>628.56792</v>
+        <v>837.3162372000002</v>
       </c>
       <c r="N94">
-        <v>157.23208</v>
+        <v>-51.51623720000021</v>
       </c>
       <c r="O94">
-        <v>46.3834636</v>
+        <v>-15.19728997400006</v>
       </c>
       <c r="P94">
-        <v>110.8486164</v>
+        <v>-36.31894722600015</v>
       </c>
       <c r="Q94">
-        <v>213.3486164</v>
+        <v>66.18105277399985</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4526684031474967</v>
+        <v>0.5196822666976045</v>
       </c>
       <c r="T94">
-        <v>6.294124797033629</v>
+        <v>7.33080795319126</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.295</v>
+        <v>0.2768499996789504</v>
       </c>
       <c r="W94">
-        <v>0.06345000000000001</v>
+        <v>0.08576559003807649</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.250143341709198</v>
+        <v>0.9384745751828827</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1161397574042434</v>
+        <v>0.1168677574042434</v>
       </c>
       <c r="C95">
-        <v>-1457.183559261845</v>
+        <v>-1573.804913901624</v>
       </c>
       <c r="D95">
-        <v>5368.118440738155</v>
+        <v>5327.411086098376</v>
       </c>
       <c r="E95">
-        <v>7001.102000000001</v>
+        <v>7077.016000000001</v>
       </c>
       <c r="F95">
-        <v>7060.002</v>
+        <v>7135.916</v>
       </c>
       <c r="G95">
         <v>234.7</v>
@@ -9208,37 +9208,37 @@
         <v>785.8</v>
       </c>
       <c r="M95">
-        <v>837.3162372000002</v>
+        <v>846.3196376000001</v>
       </c>
       <c r="N95">
-        <v>-51.51623720000021</v>
+        <v>-60.51963760000012</v>
       </c>
       <c r="O95">
-        <v>-15.19728997400006</v>
+        <v>-17.85329309200004</v>
       </c>
       <c r="P95">
-        <v>-36.31894722600015</v>
+        <v>-42.66634450800009</v>
       </c>
       <c r="Q95">
-        <v>66.18105277399985</v>
+        <v>59.83365549199991</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5196822666976045</v>
+        <v>0.5986626444805387</v>
       </c>
       <c r="T95">
-        <v>7.33080795319126</v>
+        <v>8.552609278723139</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.2768499996789504</v>
+        <v>0.2739047869164084</v>
       </c>
       <c r="W95">
-        <v>0.08576559003807649</v>
+        <v>0.08611489227171397</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9384745751828827</v>
+        <v>0.9284908031064691</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1168677574042434</v>
+        <v>0.1175957574042434</v>
       </c>
       <c r="C96">
-        <v>-1573.804913901624</v>
+        <v>-1689.813533436057</v>
       </c>
       <c r="D96">
-        <v>5327.411086098376</v>
+        <v>5287.316466563943</v>
       </c>
       <c r="E96">
-        <v>7077.016000000001</v>
+        <v>7152.93</v>
       </c>
       <c r="F96">
-        <v>7135.916</v>
+        <v>7211.83</v>
       </c>
       <c r="G96">
         <v>234.7</v>
@@ -9290,37 +9290,37 @@
         <v>785.8</v>
       </c>
       <c r="M96">
-        <v>846.3196376000001</v>
+        <v>855.3230380000001</v>
       </c>
       <c r="N96">
-        <v>-60.51963760000012</v>
+        <v>-69.52303800000016</v>
       </c>
       <c r="O96">
-        <v>-17.85329309200004</v>
+        <v>-20.50929621000004</v>
       </c>
       <c r="P96">
-        <v>-42.66634450800009</v>
+        <v>-49.01374179000011</v>
       </c>
       <c r="Q96">
-        <v>59.83365549199991</v>
+        <v>53.48625820999989</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5986626444805387</v>
+        <v>0.7092351733766468</v>
       </c>
       <c r="T96">
-        <v>8.552609278723139</v>
+        <v>10.26313113446777</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.2739047869164084</v>
+        <v>0.2710215786330777</v>
       </c>
       <c r="W96">
-        <v>0.08611489227171397</v>
+        <v>0.08645684077411699</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9284908031064691</v>
+        <v>0.9187172157053484</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1175957574042434</v>
+        <v>0.1183237574042434</v>
       </c>
       <c r="C97">
-        <v>-1689.813533436057</v>
+        <v>-1805.223149036903</v>
       </c>
       <c r="D97">
-        <v>5287.316466563943</v>
+        <v>5247.820850963098</v>
       </c>
       <c r="E97">
-        <v>7152.93</v>
+        <v>7228.844000000001</v>
       </c>
       <c r="F97">
-        <v>7211.83</v>
+        <v>7287.744000000001</v>
       </c>
       <c r="G97">
         <v>234.7</v>
@@ -9372,37 +9372,37 @@
         <v>785.8</v>
       </c>
       <c r="M97">
-        <v>855.3230380000001</v>
+        <v>864.3264384000001</v>
       </c>
       <c r="N97">
-        <v>-69.52303800000016</v>
+        <v>-78.52643840000019</v>
       </c>
       <c r="O97">
-        <v>-20.50929621000004</v>
+        <v>-23.16529932800005</v>
       </c>
       <c r="P97">
-        <v>-49.01374179000011</v>
+        <v>-55.36113907200014</v>
       </c>
       <c r="Q97">
-        <v>53.48625820999989</v>
+        <v>47.13886092799986</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7092351733766468</v>
+        <v>0.8750939667208091</v>
       </c>
       <c r="T97">
-        <v>10.26313113446777</v>
+        <v>12.82891391808472</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.2710215786330777</v>
+        <v>0.2681984371889832</v>
       </c>
       <c r="W97">
-        <v>0.08645684077411699</v>
+        <v>0.08679166534938661</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9187172157053484</v>
+        <v>0.9091472447084176</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1183237574042434</v>
+        <v>0.1190517574042435</v>
       </c>
       <c r="C98">
-        <v>-1805.223149036902</v>
+        <v>-1920.047084637165</v>
       </c>
       <c r="D98">
-        <v>5247.820850963098</v>
+        <v>5208.910915362834</v>
       </c>
       <c r="E98">
-        <v>7228.844</v>
+        <v>7304.758</v>
       </c>
       <c r="F98">
-        <v>7287.744</v>
+        <v>7363.657999999999</v>
       </c>
       <c r="G98">
         <v>234.7</v>
@@ -9454,37 +9454,37 @@
         <v>785.8</v>
       </c>
       <c r="M98">
-        <v>864.3264384</v>
+        <v>873.3298388000001</v>
       </c>
       <c r="N98">
-        <v>-78.52643840000007</v>
+        <v>-87.52983880000011</v>
       </c>
       <c r="O98">
-        <v>-23.16529932800002</v>
+        <v>-25.82130244600003</v>
       </c>
       <c r="P98">
-        <v>-55.36113907200006</v>
+        <v>-61.70853635400007</v>
       </c>
       <c r="Q98">
-        <v>47.13886092799994</v>
+        <v>40.79146364599993</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8750939667208067</v>
+        <v>1.151525288961076</v>
       </c>
       <c r="T98">
-        <v>12.82891391808469</v>
+        <v>17.10521855744625</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.2681984371889832</v>
+        <v>0.2654335048468287</v>
       </c>
       <c r="W98">
-        <v>0.08679166534938661</v>
+        <v>0.08711958632516613</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9091472447084177</v>
+        <v>0.8997745927011144</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1190517574042435</v>
+        <v>0.1197797574042434</v>
       </c>
       <c r="C99">
-        <v>-1920.047084637165</v>
+        <v>-2034.298271917326</v>
       </c>
       <c r="D99">
-        <v>5208.910915362834</v>
+        <v>5170.573728082673</v>
       </c>
       <c r="E99">
-        <v>7304.758</v>
+        <v>7380.672</v>
       </c>
       <c r="F99">
-        <v>7363.657999999999</v>
+        <v>7439.571999999999</v>
       </c>
       <c r="G99">
         <v>234.7</v>
@@ -9536,37 +9536,37 @@
         <v>785.8</v>
       </c>
       <c r="M99">
-        <v>873.3298388000001</v>
+        <v>882.3332392</v>
       </c>
       <c r="N99">
-        <v>-87.52983880000011</v>
+        <v>-96.53323920000003</v>
       </c>
       <c r="O99">
-        <v>-25.82130244600003</v>
+        <v>-28.47730556400001</v>
       </c>
       <c r="P99">
-        <v>-61.70853635400007</v>
+        <v>-68.05593363600002</v>
       </c>
       <c r="Q99">
-        <v>40.79146364599993</v>
+        <v>34.44406636399998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.151525288961076</v>
+        <v>1.704387933441613</v>
       </c>
       <c r="T99">
-        <v>17.10521855744625</v>
+        <v>25.65782783616937</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.2654335048468287</v>
+        <v>0.2627249996953305</v>
       </c>
       <c r="W99">
-        <v>0.08711958632516613</v>
+        <v>0.08744081503613381</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8997745927011144</v>
+        <v>0.8905932193062052</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1197797574042434</v>
+        <v>0.1205077574042434</v>
       </c>
       <c r="C100">
-        <v>-2034.298271917326</v>
+        <v>-2147.989264634623</v>
       </c>
       <c r="D100">
-        <v>5170.573728082673</v>
+        <v>5132.796735365377</v>
       </c>
       <c r="E100">
-        <v>7380.672</v>
+        <v>7456.586</v>
       </c>
       <c r="F100">
-        <v>7439.571999999999</v>
+        <v>7515.486</v>
       </c>
       <c r="G100">
         <v>234.7</v>
@@ -9618,37 +9618,37 @@
         <v>785.8</v>
       </c>
       <c r="M100">
-        <v>882.3332392</v>
+        <v>891.3366396</v>
       </c>
       <c r="N100">
-        <v>-96.53323920000003</v>
+        <v>-105.5366396000001</v>
       </c>
       <c r="O100">
-        <v>-28.47730556400001</v>
+        <v>-31.13330868200002</v>
       </c>
       <c r="P100">
-        <v>-68.05593363600002</v>
+        <v>-74.40333091800004</v>
       </c>
       <c r="Q100">
-        <v>34.44406636399998</v>
+        <v>28.09666908199996</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.704387933441613</v>
+        <v>3.362975866883227</v>
       </c>
       <c r="T100">
-        <v>25.65782783616937</v>
+        <v>51.31565567233875</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.2627249996953305</v>
+        <v>0.2600712118196201</v>
       </c>
       <c r="W100">
-        <v>0.08744081503613381</v>
+        <v>0.08775555427819308</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8905932193062052</v>
+        <v>0.881597328202102</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1205077574042434</v>
-      </c>
-      <c r="C101">
-        <v>-2147.989264634623</v>
-      </c>
-      <c r="D101">
-        <v>5132.796735365377</v>
-      </c>
-      <c r="E101">
-        <v>7456.586</v>
-      </c>
-      <c r="F101">
-        <v>7515.486</v>
-      </c>
-      <c r="G101">
-        <v>234.7</v>
-      </c>
-      <c r="H101">
-        <v>7532.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>888.3</v>
-      </c>
-      <c r="K101">
-        <v>102.5</v>
-      </c>
-      <c r="L101">
-        <v>785.8</v>
-      </c>
-      <c r="M101">
-        <v>891.3366396</v>
-      </c>
-      <c r="N101">
-        <v>-105.5366396000001</v>
-      </c>
-      <c r="O101">
-        <v>-31.13330868200002</v>
-      </c>
-      <c r="P101">
-        <v>-74.40333091800004</v>
-      </c>
-      <c r="Q101">
-        <v>28.09666908199996</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.362975866883227</v>
-      </c>
-      <c r="T101">
-        <v>51.31565567233875</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.2600712118196201</v>
-      </c>
-      <c r="W101">
-        <v>0.08775555427819308</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.881597328202102</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
